--- a/output/yearly_surface_area_iteration_16_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_16_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497609844425</v>
+        <v>10.84497613882621</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907112734046</v>
+        <v>37.78907126805048</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.197773256910113</v>
+        <v>6.094689747964199</v>
       </c>
       <c r="C2" t="n">
-        <v>6.351907646476863</v>
+        <v>12.19625172985812</v>
       </c>
       <c r="D2" t="n">
-        <v>27.28178695331462</v>
+        <v>34.39847606139974</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.42387832852314</v>
+        <v>18.60902773399829</v>
       </c>
       <c r="C3" t="n">
-        <v>26.30592973529329</v>
+        <v>27.67546778271759</v>
       </c>
       <c r="D3" t="n">
-        <v>84.00324231387833</v>
+        <v>105.9502122423158</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.69656751059227</v>
+        <v>39.89626320518188</v>
       </c>
       <c r="C4" t="n">
-        <v>64.13266877992288</v>
+        <v>70.78204598078653</v>
       </c>
       <c r="D4" t="n">
-        <v>94.25268834621504</v>
+        <v>147.0648243484679</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.85390918517903</v>
+        <v>50.65818153913543</v>
       </c>
       <c r="C5" t="n">
-        <v>121.810346404423</v>
+        <v>117.0979574240383</v>
       </c>
       <c r="D5" t="n">
-        <v>63.81360077604268</v>
+        <v>106.1760142142926</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.16486116551801</v>
+        <v>47.97997380195012</v>
       </c>
       <c r="C6" t="n">
-        <v>149.6959081958494</v>
+        <v>124.8606365215179</v>
       </c>
       <c r="D6" t="n">
-        <v>46.0478943199924</v>
+        <v>59.4516957260741</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.930902112271</v>
+        <v>33.65627479698915</v>
       </c>
       <c r="C7" t="n">
-        <v>127.6183658227471</v>
+        <v>103.1247423494934</v>
       </c>
       <c r="D7" t="n">
-        <v>38.74663664350886</v>
+        <v>41.62119392154352</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.60211444233956</v>
+        <v>16.77315952705676</v>
       </c>
       <c r="C8" t="n">
-        <v>82.86441497695203</v>
+        <v>69.42919764433444</v>
       </c>
       <c r="D8" t="n">
-        <v>35.9663271450819</v>
+        <v>35.63253292563798</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.09999939711293</v>
+        <v>7.876561831172157</v>
       </c>
       <c r="C9" t="n">
-        <v>44.26405874137593</v>
+        <v>41.04687151455913</v>
       </c>
       <c r="D9" t="n">
-        <v>33.9468721174462</v>
+        <v>33.61405964570653</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.409429850399925</v>
+        <v>5.551783267515713</v>
       </c>
       <c r="C10" t="n">
-        <v>31.31775176547326</v>
+        <v>30.17892442854695</v>
       </c>
       <c r="D10" t="n">
-        <v>34.87658719336794</v>
+        <v>34.44952694202058</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>28.43141351498762</v>
       </c>
       <c r="D11" t="n">
-        <v>35.7169632282032</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>27.33774657245668</v>
+        <v>26.68684784454105</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>33.84673385161303</v>
       </c>
     </row>
     <row r="13">
@@ -934,10 +934,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>25.49598787928967</v>
+        <v>24.45533531278805</v>
       </c>
       <c r="D13" t="n">
         <v>32.26022956155019</v>
@@ -951,10 +951,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>22.73924032576462</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -962,13 +962,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>20.42526098685489</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>18.59921025695582</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -996,7 +996,7 @@
         <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>23.13881164139307</v>
       </c>
     </row>
     <row r="18">
@@ -1010,7 +1010,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1024,7 +1024,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.668991898122866</v>
+        <v>7.626667730977979</v>
       </c>
       <c r="C21" t="n">
-        <v>92.98652676473974</v>
+        <v>91.52001277173574</v>
       </c>
       <c r="D21" t="n">
-        <v>8.627615885388224</v>
+        <v>7.626667730977979</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.364490440182824</v>
+        <v>8.015970005175207</v>
       </c>
       <c r="C2" t="n">
-        <v>4.614214209960009</v>
+        <v>7.826492698255572</v>
       </c>
       <c r="D2" t="n">
-        <v>32.36429481820035</v>
+        <v>28.90363416073034</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.84112110282804</v>
+        <v>19.17844140246144</v>
       </c>
       <c r="C3" t="n">
-        <v>25.57943643415064</v>
+        <v>37.00697971158352</v>
       </c>
       <c r="D3" t="n">
-        <v>85.19606577453821</v>
+        <v>107.4522862298134</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.31819373382976</v>
+        <v>37.13951565165684</v>
       </c>
       <c r="C4" t="n">
-        <v>64.14543150007809</v>
+        <v>69.8376046893011</v>
       </c>
       <c r="D4" t="n">
-        <v>109.5424270921549</v>
+        <v>162.3162749339421</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>51.56629816556373</v>
+        <v>54.78152189697203</v>
       </c>
       <c r="C5" t="n">
-        <v>118.7914722138641</v>
+        <v>121.7367153266045</v>
       </c>
       <c r="D5" t="n">
-        <v>79.88971943308421</v>
+        <v>127.3572209334175</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.75104666041137</v>
+        <v>56.43282153551517</v>
       </c>
       <c r="C6" t="n">
-        <v>170.3450076592726</v>
+        <v>150.8632062161989</v>
       </c>
       <c r="D6" t="n">
-        <v>53.41394734495622</v>
+        <v>75.14984151698062</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>35.45287309576081</v>
+        <v>43.59745205019235</v>
       </c>
       <c r="C7" t="n">
-        <v>167.3231882256009</v>
+        <v>137.8589761257456</v>
       </c>
       <c r="D7" t="n">
-        <v>42.69915290080652</v>
+        <v>47.19064864773568</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19.94420461177395</v>
+        <v>25.03456645829366</v>
       </c>
       <c r="C8" t="n">
-        <v>122.8362727553609</v>
+        <v>98.55274329081605</v>
       </c>
       <c r="D8" t="n">
-        <v>37.71874679716245</v>
+        <v>38.30288668118931</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>11.6484365108884</v>
       </c>
       <c r="C9" t="n">
-        <v>70.22343153707007</v>
+        <v>61.01561981893925</v>
       </c>
       <c r="D9" t="n">
-        <v>35.49999698556465</v>
+        <v>34.61249706092553</v>
       </c>
     </row>
     <row r="10">
@@ -1203,10 +1203,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.121196935978863</v>
+        <v>6.548257187326225</v>
       </c>
       <c r="C10" t="n">
-        <v>41.28249096357838</v>
+        <v>38.15071578703105</v>
       </c>
       <c r="D10" t="n">
         <v>35.16129402759952</v>
@@ -1220,10 +1220,10 @@
         <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>32.51842920776709</v>
+        <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>30.15830772675777</v>
+        <v>29.50740899884213</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>34.49763257952867</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>27.57729301229291</v>
+        <v>26.53664044579129</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>32.26022956155019</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>25.19753657719863</v>
+        <v>24.58296251434014</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -1273,10 +1273,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>22.57528845915541</v>
+        <v>21.85861263505523</v>
       </c>
       <c r="D15" t="n">
         <v>29.38370878810703</v>
@@ -1287,13 +1287,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>20.25247339090745</v>
+        <v>19.83915760741954</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>23.13881164139307</v>
       </c>
     </row>
     <row r="18">
@@ -1321,7 +1321,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.843052476960547</v>
+        <v>7.792835434129308</v>
       </c>
       <c r="C21" t="n">
-        <v>100.979300640867</v>
+        <v>99.35865178514868</v>
       </c>
       <c r="D21" t="n">
-        <v>9.803815596200684</v>
+        <v>8.766939863395471</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.486227155509429</v>
+        <v>9.619164006210248</v>
       </c>
       <c r="C2" t="n">
-        <v>12.28853601405732</v>
+        <v>7.992408060273283</v>
       </c>
       <c r="D2" t="n">
-        <v>32.52530144169683</v>
+        <v>42.80910864368217</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.02689240310894</v>
+        <v>21.8389776809703</v>
       </c>
       <c r="C3" t="n">
-        <v>21.8684301120977</v>
+        <v>34.06664533736432</v>
       </c>
       <c r="D3" t="n">
-        <v>88.93652452771856</v>
+        <v>106.0532957512617</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.60348140513808</v>
+        <v>35.7483791547391</v>
       </c>
       <c r="C4" t="n">
-        <v>63.18822748843746</v>
+        <v>78.3503390328252</v>
       </c>
       <c r="D4" t="n">
-        <v>121.2713669147915</v>
+        <v>171.5437216061579</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>53.45616249623884</v>
+        <v>54.58517235612267</v>
       </c>
       <c r="C5" t="n">
-        <v>118.202423591316</v>
+        <v>122.963899956913</v>
       </c>
       <c r="D5" t="n">
-        <v>96.28490609400595</v>
+        <v>147.0903497887784</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>57.3586096206199</v>
+        <v>62.83283481950012</v>
       </c>
       <c r="C6" t="n">
-        <v>176.8255242550058</v>
+        <v>166.8431135982242</v>
       </c>
       <c r="D6" t="n">
-        <v>62.59132488425541</v>
+        <v>92.13604029585892</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>44.79518424937346</v>
+        <v>52.58044354405067</v>
       </c>
       <c r="C7" t="n">
-        <v>199.3625245536955</v>
+        <v>170.8564982131851</v>
       </c>
       <c r="D7" t="n">
-        <v>47.25053525769474</v>
+        <v>54.43692845278139</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>27.28767743954009</v>
+        <v>33.54631905411351</v>
       </c>
       <c r="C8" t="n">
-        <v>164.8943444052942</v>
+        <v>131.4314739060417</v>
       </c>
       <c r="D8" t="n">
-        <v>39.72151211382594</v>
+        <v>41.39048321104552</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>13.97812381306608</v>
+        <v>16.86249856814321</v>
       </c>
       <c r="C9" t="n">
-        <v>103.1718662392973</v>
+        <v>85.08905527477528</v>
       </c>
       <c r="D9" t="n">
-        <v>36.94218436310322</v>
+        <v>35.83280945730432</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>8.398851609831464</v>
       </c>
       <c r="C10" t="n">
-        <v>58.0801941832413</v>
+        <v>51.38958357879929</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>35.87306111317846</v>
       </c>
     </row>
     <row r="11">
@@ -1531,10 +1531,10 @@
         <v>5.153193699591506</v>
       </c>
       <c r="C11" t="n">
-        <v>38.91549724863931</v>
+        <v>36.78314123501524</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>32.76190263842031</v>
+        <v>31.89403766786613</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>28.87810872041993</v>
       </c>
       <c r="D13" t="n">
-        <v>33.56104526967722</v>
+        <v>32.26022956155019</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>27.3485457972034</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -1584,10 +1584,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>24.00864010735575</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
         <v>29.38370878810703</v>
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.49242074137117</v>
+        <v>20.66578917439536</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>23.13881164139307</v>
       </c>
     </row>
     <row r="18">
@@ -1629,10 +1629,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1646,7 +1646,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.001257657861498</v>
+        <v>7.943568409209668</v>
       </c>
       <c r="C21" t="n">
-        <v>108.0169783811302</v>
+        <v>106.2452274731793</v>
       </c>
       <c r="D21" t="n">
-        <v>11.00172927955956</v>
+        <v>9.929460511512085</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.856926877087224</v>
+        <v>8.745408549430588</v>
       </c>
       <c r="C2" t="n">
-        <v>8.552004251693965</v>
+        <v>5.62639609303847</v>
       </c>
       <c r="D2" t="n">
-        <v>26.87337990834794</v>
+        <v>35.46858105902876</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>26.31574721233575</v>
+        <v>25.10819753611218</v>
       </c>
       <c r="C3" t="n">
-        <v>37.64511571934394</v>
+        <v>49.55371537185776</v>
       </c>
       <c r="D3" t="n">
-        <v>95.43569432983244</v>
+        <v>116.6021748333937</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.67859295227957</v>
+        <v>26.21462719879833</v>
       </c>
       <c r="C4" t="n">
-        <v>92.97641633069418</v>
+        <v>102.7398972494287</v>
       </c>
       <c r="D4" t="n">
-        <v>113.7668874635289</v>
+        <v>163.9371403936536</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.29949946972007</v>
+        <v>35.39200473809752</v>
       </c>
       <c r="C5" t="n">
-        <v>105.660596669563</v>
+        <v>99.69647936626362</v>
       </c>
       <c r="D5" t="n">
-        <v>63.27363953870694</v>
+        <v>93.16785713302231</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>27.81389420901639</v>
+        <v>32.6440929139107</v>
       </c>
       <c r="C6" t="n">
-        <v>131.3009014613769</v>
+        <v>112.5033781681633</v>
       </c>
       <c r="D6" t="n">
-        <v>31.11452999069417</v>
+        <v>35.82397372796611</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.08575620763474</v>
+        <v>22.21793229480956</v>
       </c>
       <c r="C7" t="n">
-        <v>115.9404768807313</v>
+        <v>92.40503916682252</v>
       </c>
       <c r="D7" t="n">
-        <v>27.90716024091983</v>
+        <v>29.10489244010094</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.680032363873551</v>
+        <v>11.68279768053704</v>
       </c>
       <c r="C8" t="n">
-        <v>76.02163347835176</v>
+        <v>62.66986470059513</v>
       </c>
       <c r="D8" t="n">
-        <v>27.20422888467911</v>
+        <v>26.36974333606933</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.324999547834698</v>
+        <v>5.990624491314035</v>
       </c>
       <c r="C9" t="n">
-        <v>44.26405874137593</v>
+        <v>39.160934174701</v>
       </c>
       <c r="D9" t="n">
-        <v>27.17968519207294</v>
+        <v>27.29062268265283</v>
       </c>
     </row>
     <row r="10">
@@ -1828,10 +1828,10 @@
         <v>3.701188845010476</v>
       </c>
       <c r="C10" t="n">
-        <v>30.46363126277853</v>
+        <v>28.75539025738908</v>
       </c>
       <c r="D10" t="n">
-        <v>28.61303684027329</v>
+        <v>28.18597658892593</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>26.12136116689488</v>
+        <v>25.58827216348886</v>
       </c>
       <c r="D11" t="n">
-        <v>28.43141351498762</v>
+        <v>28.07602084605028</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.169662426385451</v>
+        <v>1.952696183746906</v>
       </c>
       <c r="C12" t="n">
-        <v>24.30021917551705</v>
+        <v>23.43235420496287</v>
       </c>
       <c r="D12" t="n">
-        <v>27.33774657245668</v>
+        <v>26.25291535926396</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>22.63419332141022</v>
+        <v>21.853703896534</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>24.97566159603886</v>
       </c>
     </row>
     <row r="14">
@@ -1881,10 +1881,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>19.97365704290136</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
         <v>24.58296251434014</v>
@@ -1895,13 +1895,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0.3583379120500857</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
-        <v>21.85861263505523</v>
+        <v>22.57528845915541</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>16.11931555602838</v>
       </c>
       <c r="D16" t="n">
-        <v>20.25247339090745</v>
+        <v>19.83915760741954</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.58328130950962</v>
+        <v>15.11106066376691</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>17.47216389248049</v>
       </c>
     </row>
     <row r="18">
@@ -1943,7 +1943,7 @@
         <v>16.05157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>13.37631247036279</v>
       </c>
     </row>
     <row r="19">
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>72.62969516017901</v>
+        <v>71.95719798276996</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>6.724971774090649</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.865541622247192</v>
+        <v>5.223879534297278</v>
       </c>
       <c r="C2" t="n">
-        <v>4.232314353007999</v>
+        <v>2.532909076956771</v>
       </c>
       <c r="D2" t="n">
-        <v>18.60608249088555</v>
+        <v>24.7626223442173</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>27.27785996249763</v>
+        <v>27.83745615391831</v>
       </c>
       <c r="C3" t="n">
-        <v>36.25594271783471</v>
+        <v>36.71245540030947</v>
       </c>
       <c r="D3" t="n">
-        <v>96.14746141541139</v>
+        <v>117.8440856792659</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.86324363613598</v>
+        <v>34.9953786655818</v>
       </c>
       <c r="C4" t="n">
-        <v>95.92460468654734</v>
+        <v>115.0814476395154</v>
       </c>
       <c r="D4" t="n">
-        <v>130.7413052699562</v>
+        <v>182.1495420551362</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.05468443846411</v>
+        <v>38.65631585471817</v>
       </c>
       <c r="C5" t="n">
-        <v>138.0091835244954</v>
+        <v>140.9298829446297</v>
       </c>
       <c r="D5" t="n">
-        <v>82.56498192715677</v>
+        <v>117.6870060465864</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.40887437551896</v>
+        <v>38.35982804803563</v>
       </c>
       <c r="C6" t="n">
-        <v>152.1512592041707</v>
+        <v>136.050596854523</v>
       </c>
       <c r="D6" t="n">
-        <v>37.91705983342032</v>
+        <v>46.53091419048183</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.88802400845363</v>
+        <v>20.54110721595601</v>
       </c>
       <c r="C7" t="n">
-        <v>147.0815140594401</v>
+        <v>117.9766216193392</v>
       </c>
       <c r="D7" t="n">
-        <v>30.3625112492411</v>
+        <v>32.03933632809466</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.17795837637593</v>
+        <v>9.680032363873551</v>
       </c>
       <c r="C8" t="n">
-        <v>100.1382658331747</v>
+        <v>82.28027509292518</v>
       </c>
       <c r="D8" t="n">
-        <v>27.95526587842792</v>
+        <v>26.95388322009618</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.437499623195581</v>
+        <v>4.548437113775471</v>
       </c>
       <c r="C9" t="n">
-        <v>49.58905828921062</v>
+        <v>42.26718391093791</v>
       </c>
       <c r="D9" t="n">
-        <v>28.17812260729194</v>
+        <v>28.39999758845172</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>32.59893251951534</v>
+        <v>31.17539834835747</v>
       </c>
       <c r="D10" t="n">
-        <v>29.89421759431538</v>
+        <v>29.18245050873644</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.421570675749381</v>
       </c>
       <c r="C11" t="n">
+        <v>28.07602084605028</v>
+      </c>
+      <c r="D11" t="n">
         <v>28.96450251839364</v>
-      </c>
-      <c r="D11" t="n">
-        <v>29.67528785626833</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>20.61179305066178</v>
+        <v>19.52696183746906</v>
       </c>
       <c r="D12" t="n">
-        <v>28.20561154301086</v>
+        <v>27.55471281509523</v>
       </c>
     </row>
     <row r="13">
@@ -2178,10 +2178,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>16.3902779224005</v>
+        <v>15.86995163914969</v>
       </c>
       <c r="D13" t="n">
         <v>25.75615102091507</v>
@@ -2192,13 +2192,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>14.74977750860408</v>
       </c>
       <c r="D14" t="n">
-        <v>18.12993485432585</v>
+        <v>18.74450891718435</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>16.84188186635403</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.22610507161303</v>
+        <v>12.81278928812512</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2240,7 +2240,7 @@
         <v>13.69439872653876</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>11.33329549782518</v>
       </c>
     </row>
     <row r="18">
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>63.19019098384595</v>
+        <v>62.58837964114266</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>5.416302084329653</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.093307089632453</v>
+        <v>6.378414834491527</v>
       </c>
       <c r="C2" t="n">
-        <v>6.085854018625978</v>
+        <v>7.102944640225672</v>
       </c>
       <c r="D2" t="n">
-        <v>14.70069012339174</v>
+        <v>25.40763058590745</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.8831563276614</v>
+        <v>23.03180114163017</v>
       </c>
       <c r="C3" t="n">
-        <v>26.03594911662541</v>
+        <v>22.93853510972673</v>
       </c>
       <c r="D3" t="n">
-        <v>89.26050127012</v>
+        <v>111.8652421604028</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.71231653158923</v>
+        <v>42.83168884087984</v>
       </c>
       <c r="C4" t="n">
-        <v>93.12956897255668</v>
+        <v>103.4418468579652</v>
       </c>
       <c r="D4" t="n">
-        <v>146.2224848182242</v>
+        <v>193.9422954785489</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.98229715025711</v>
+        <v>44.76769531365456</v>
       </c>
       <c r="C5" t="n">
-        <v>156.5396714421539</v>
+        <v>175.6101205971482</v>
       </c>
       <c r="D5" t="n">
-        <v>105.9796646734432</v>
+        <v>149.8146996680633</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.09064925062275</v>
+        <v>44.35732477327939</v>
       </c>
       <c r="C6" t="n">
-        <v>184.9161070857038</v>
+        <v>174.9336964289222</v>
       </c>
       <c r="D6" t="n">
-        <v>51.44161620712438</v>
+        <v>66.97875537453442</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.930902112271</v>
+        <v>30.18285141936394</v>
       </c>
       <c r="C7" t="n">
-        <v>181.8756344456513</v>
+        <v>153.7888143748544</v>
       </c>
       <c r="D7" t="n">
-        <v>33.59638818703009</v>
+        <v>36.77037851486003</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.76624623539802</v>
+        <v>14.01935721664445</v>
       </c>
       <c r="C8" t="n">
-        <v>142.112888928247</v>
+        <v>114.407968714402</v>
       </c>
       <c r="D8" t="n">
-        <v>29.45733986592554</v>
+        <v>29.12354564648163</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>6.101561981893925</v>
       </c>
       <c r="C9" t="n">
-        <v>80.31874317984003</v>
+        <v>66.34061936677394</v>
       </c>
       <c r="D9" t="n">
-        <v>29.17656002251095</v>
+        <v>28.84374755077128</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.704714925199962</v>
+        <v>2.562361508084175</v>
       </c>
       <c r="C10" t="n">
-        <v>43.56014563743098</v>
+        <v>39.14718970684157</v>
       </c>
       <c r="D10" t="n">
-        <v>30.17892442854695</v>
+        <v>29.75186417719959</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.421570675749381</v>
       </c>
       <c r="C11" t="n">
-        <v>32.87382187670443</v>
+        <v>31.62994753542373</v>
       </c>
       <c r="D11" t="n">
-        <v>30.20837685967435</v>
+        <v>29.49759152179966</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>23.64932044760141</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>27.98864530037232</v>
       </c>
     </row>
     <row r="13">
@@ -2489,13 +2489,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.2601631416254048</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>18.73174619702914</v>
+        <v>17.69109363052753</v>
       </c>
       <c r="D13" t="n">
-        <v>26.53664044579129</v>
+        <v>26.01631416254048</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>15.67163860289184</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>19.35908298004286</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>15.40853021815369</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>16.48354395430394</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.05273663858884</v>
+        <v>13.63942085510094</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -2551,7 +2551,7 @@
         <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>10.38885420633975</v>
       </c>
     </row>
     <row r="18">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>33.7014351913845</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>3.610868056219768</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.046363126277853</v>
+        <v>3.843542262126263</v>
       </c>
       <c r="C2" t="n">
-        <v>2.889283493598362</v>
+        <v>3.455751918948773</v>
       </c>
       <c r="D2" t="n">
-        <v>10.27497147264712</v>
+        <v>17.72741829558466</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.92242623583128</v>
+        <v>24.15590226299277</v>
       </c>
       <c r="C3" t="n">
-        <v>26.72317250959818</v>
+        <v>26.33538216642069</v>
       </c>
       <c r="D3" t="n">
-        <v>85.61821728736433</v>
+        <v>110.9325818413683</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>47.97506506342888</v>
+        <v>47.33692905566846</v>
       </c>
       <c r="C4" t="n">
-        <v>92.07026319967437</v>
+        <v>97.76243638889737</v>
       </c>
       <c r="D4" t="n">
-        <v>156.738966226116</v>
+        <v>207.2155244399658</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.96404485450392</v>
+        <v>46.75573441475435</v>
       </c>
       <c r="C5" t="n">
-        <v>185.4766850248287</v>
+        <v>210.0694650162113</v>
       </c>
       <c r="D5" t="n">
-        <v>112.1892189028043</v>
+        <v>156.4660403643354</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.00006641992479</v>
+        <v>35.94472869558847</v>
       </c>
       <c r="C6" t="n">
-        <v>222.1891404251382</v>
+        <v>201.4595376499668</v>
       </c>
       <c r="D6" t="n">
-        <v>50.39507315439728</v>
+        <v>63.79887456047898</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.785259294677205</v>
+        <v>9.282424543653592</v>
       </c>
       <c r="C7" t="n">
-        <v>188.3433883212293</v>
+        <v>155.0464331839945</v>
       </c>
       <c r="D7" t="n">
-        <v>33.77604801690726</v>
+        <v>35.99185258539232</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.922082078466008</v>
+        <v>4.172427743048944</v>
       </c>
       <c r="C8" t="n">
-        <v>102.3079282595601</v>
+        <v>81.36234098945441</v>
       </c>
       <c r="D8" t="n">
-        <v>31.2097595180061</v>
+        <v>31.04286240828414</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>33.17030968338697</v>
+        <v>29.84218496599028</v>
       </c>
       <c r="D9" t="n">
-        <v>31.61718481526852</v>
+        <v>30.84062238120929</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>0.9964739198105126</v>
       </c>
       <c r="C10" t="n">
-        <v>25.76596849795754</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>23.63066724122073</v>
+        <v>23.06125357275758</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>19.72429312602266</v>
+        <v>18.8358114536793</v>
       </c>
       <c r="D11" t="n">
-        <v>22.92282714645877</v>
+        <v>22.38973814305275</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.18763698469816</v>
+        <v>14.31977201414398</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>21.26269177857742</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>12.74799393964483</v>
       </c>
       <c r="D13" t="n">
-        <v>15.34962535589888</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>12.90605532002857</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>13.82791641431633</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>11.82515109765283</v>
+        <v>11.46681318560274</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>12.18348900970292</v>
       </c>
     </row>
     <row r="16">
@@ -2848,7 +2848,7 @@
         <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>8.679631453246051</v>
       </c>
     </row>
     <row r="17">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>28.89283493598363</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>2.675262494072558</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.752239725631309</v>
+        <v>3.582397372796611</v>
       </c>
       <c r="C2" t="n">
-        <v>7.585964510715104</v>
+        <v>5.901285450227578</v>
       </c>
       <c r="D2" t="n">
-        <v>13.74446785945534</v>
+        <v>20.34672117051515</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.26755945936965</v>
+        <v>18.95754816900591</v>
       </c>
       <c r="C3" t="n">
-        <v>18.85937339858123</v>
+        <v>20.03256190515617</v>
       </c>
       <c r="D3" t="n">
-        <v>76.026542216873</v>
+        <v>100.8009455335413</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>45.49909735331843</v>
+        <v>46.40525048433824</v>
       </c>
       <c r="C4" t="n">
-        <v>80.40513697781377</v>
+        <v>83.44266437475339</v>
       </c>
       <c r="D4" t="n">
-        <v>162.0865459711484</v>
+        <v>213.3799182749315</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>56.15596868291757</v>
+        <v>56.59775514982863</v>
       </c>
       <c r="C5" t="n">
-        <v>179.6598298771663</v>
+        <v>198.3866673356742</v>
       </c>
       <c r="D5" t="n">
-        <v>136.0211444233956</v>
+        <v>188.0537727484765</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.98876847355934</v>
+        <v>46.12839763174064</v>
       </c>
       <c r="C6" t="n">
-        <v>256.2017896387689</v>
+        <v>257.9728624972302</v>
       </c>
       <c r="D6" t="n">
-        <v>67.66303352439442</v>
+        <v>87.02407999984578</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.0676838383308</v>
+        <v>19.16371518689774</v>
       </c>
       <c r="C7" t="n">
-        <v>247.6910187906533</v>
+        <v>210.3816607861617</v>
       </c>
       <c r="D7" t="n">
-        <v>38.98618308334508</v>
+        <v>42.87881273068369</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.17381040138069</v>
+        <v>5.674501730546564</v>
       </c>
       <c r="C8" t="n">
-        <v>160.7219166622453</v>
+        <v>129.0949143699343</v>
       </c>
       <c r="D8" t="n">
-        <v>32.87873061522568</v>
+        <v>32.54493639578176</v>
       </c>
     </row>
     <row r="9">
@@ -3058,10 +3058,10 @@
         <v>2.218749811597791</v>
       </c>
       <c r="C9" t="n">
-        <v>66.34061936677394</v>
+        <v>54.47030787472577</v>
       </c>
       <c r="D9" t="n">
-        <v>32.39374724932775</v>
+        <v>31.94999728700819</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>0.9964739198105126</v>
       </c>
       <c r="C10" t="n">
-        <v>30.89069151412589</v>
+        <v>29.04009709162065</v>
       </c>
       <c r="D10" t="n">
-        <v>24.91184799526281</v>
+        <v>23.91537407545231</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
+        <v>22.0343454741154</v>
+      </c>
+      <c r="D11" t="n">
         <v>23.27821981539612</v>
-      </c>
-      <c r="D11" t="n">
-        <v>23.63361248433346</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.35729941108361</v>
+        <v>16.27246819789088</v>
       </c>
       <c r="D12" t="n">
-        <v>21.69662426385451</v>
+        <v>21.26269177857742</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>15.34962535589888</v>
+        <v>14.56913593102267</v>
       </c>
       <c r="D13" t="n">
-        <v>15.34962535589888</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>13.52062938288707</v>
+      </c>
+      <c r="D14" t="n">
         <v>13.82791641431633</v>
-      </c>
-      <c r="D14" t="n">
-        <v>14.13520344574558</v>
       </c>
     </row>
     <row r="15">
@@ -3145,7 +3145,7 @@
         <v>12.90016483380309</v>
       </c>
       <c r="D15" t="n">
-        <v>11.82515109765283</v>
+        <v>11.46681318560274</v>
       </c>
     </row>
     <row r="16">
@@ -3159,7 +3159,7 @@
         <v>23.55899965881071</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>7.852999886270235</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.0554452019901</v>
+        <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>4.249985811684442</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.717477645355171</v>
+        <v>2.55156228333746</v>
       </c>
       <c r="C2" t="n">
-        <v>4.060508504764808</v>
+        <v>3.965278977452867</v>
       </c>
       <c r="D2" t="n">
-        <v>9.658433914380121</v>
+        <v>15.06491852166731</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.95201753567892</v>
+        <v>16.35591675275186</v>
       </c>
       <c r="C3" t="n">
-        <v>24.03318379996192</v>
+        <v>21.45118733779281</v>
       </c>
       <c r="D3" t="n">
-        <v>71.74121348783568</v>
+        <v>95.58295648546947</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.04490801915065</v>
+        <v>43.38048580755381</v>
       </c>
       <c r="C4" t="n">
-        <v>67.92319666601983</v>
+        <v>72.05831799630738</v>
       </c>
       <c r="D4" t="n">
-        <v>163.1458517440307</v>
+        <v>215.0135464547982</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>62.04645490839843</v>
+        <v>61.72738690451821</v>
       </c>
       <c r="C5" t="n">
-        <v>173.9166058073225</v>
+        <v>187.2192871998668</v>
       </c>
       <c r="D5" t="n">
-        <v>151.7291076913446</v>
+        <v>209.4067853158447</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>50.87809302488671</v>
+        <v>53.21268906558563</v>
       </c>
       <c r="C6" t="n">
-        <v>278.501206993031</v>
+        <v>288.3628626821902</v>
       </c>
       <c r="D6" t="n">
-        <v>82.2341329508256</v>
+        <v>104.6945569285841</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.27108553955913</v>
+        <v>16.94791061841269</v>
       </c>
       <c r="C7" t="n">
-        <v>295.9596264176519</v>
+        <v>263.8005168696392</v>
       </c>
       <c r="D7" t="n">
-        <v>43.41779222031519</v>
+        <v>48.62792728675301</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.255876297909922</v>
+        <v>4.589670517353839</v>
       </c>
       <c r="C8" t="n">
-        <v>204.3655108545373</v>
+        <v>165.7288299539041</v>
       </c>
       <c r="D8" t="n">
-        <v>33.88011327355743</v>
+        <v>33.79666471869644</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.664062358698343</v>
+        <v>1.553124868118454</v>
       </c>
       <c r="C9" t="n">
-        <v>75.32655610374501</v>
+        <v>59.90624491314035</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>31.61718481526852</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>31.74481201682062</v>
+        <v>29.46715734296802</v>
       </c>
       <c r="D10" t="n">
-        <v>25.33890824661018</v>
+        <v>24.34243432679967</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.7451308119901</v>
+        <v>21.32356013624072</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>23.63361248433346</v>
       </c>
     </row>
     <row r="12">
@@ -3411,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.92336692580652</v>
+        <v>15.83853571261379</v>
       </c>
       <c r="D12" t="n">
         <v>19.7439280801076</v>
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.44717823151781</v>
+        <v>11.18701508989241</v>
       </c>
       <c r="D13" t="n">
         <v>15.86995163914969</v>
@@ -3442,7 +3442,7 @@
         <v>10.75504610002381</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>10.75504610002381</v>
       </c>
     </row>
     <row r="15">
@@ -3456,7 +3456,7 @@
         <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>6.450082416901544</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.10547327717769</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.44142661401257</v>
+        <v>3.987859174650544</v>
       </c>
       <c r="C2" t="n">
-        <v>6.475607857211961</v>
+        <v>10.88660029239288</v>
       </c>
       <c r="D2" t="n">
-        <v>9.748754703170826</v>
+        <v>21.06437874231957</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.19330648674539</v>
+        <v>12.76762889372977</v>
       </c>
       <c r="C3" t="n">
-        <v>20.29272504678157</v>
+        <v>18.60411899547706</v>
       </c>
       <c r="D3" t="n">
-        <v>64.33392705929349</v>
+        <v>87.34609324683872</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.02090410589222</v>
+        <v>37.44582093538184</v>
       </c>
       <c r="C4" t="n">
-        <v>63.60939725355934</v>
+        <v>63.99227885821559</v>
       </c>
       <c r="D4" t="n">
-        <v>161.5505117246296</v>
+        <v>212.9715112299648</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>61.72738690451821</v>
+        <v>63.2245521534946</v>
       </c>
       <c r="C5" t="n">
-        <v>152.8335738586222</v>
+        <v>164.6390900021901</v>
       </c>
       <c r="D5" t="n">
-        <v>168.8851488230576</v>
+        <v>226.4891953697392</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>62.9938414429966</v>
+        <v>63.47686131348603</v>
       </c>
       <c r="C6" t="n">
-        <v>281.4395778718417</v>
+        <v>292.8307964842174</v>
       </c>
       <c r="D6" t="n">
-        <v>101.957444329144</v>
+        <v>133.1122259757123</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>30.12296480940488</v>
+        <v>31.02126395879071</v>
       </c>
       <c r="C7" t="n">
-        <v>338.7186659284175</v>
+        <v>321.950415139882</v>
       </c>
       <c r="D7" t="n">
-        <v>52.22112388429633</v>
+        <v>60.7250224984822</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.011061266653972</v>
+        <v>8.344855486097888</v>
       </c>
       <c r="C8" t="n">
-        <v>275.6305767058132</v>
+        <v>234.4904391593507</v>
       </c>
       <c r="D8" t="n">
-        <v>36.38356991938679</v>
+        <v>37.05115835827462</v>
       </c>
     </row>
     <row r="9">
@@ -3680,10 +3680,10 @@
         <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>139.4484256589212</v>
+        <v>109.1624907306113</v>
       </c>
       <c r="D9" t="n">
-        <v>33.17030968338697</v>
+        <v>32.50468473990763</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>51.10487674456772</v>
+        <v>42.70602513473626</v>
       </c>
       <c r="D10" t="n">
-        <v>26.47773558353648</v>
+        <v>25.62361508084176</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.54293184264426</v>
+        <v>25.23287949455151</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>23.81130881880213</v>
       </c>
     </row>
     <row r="12">
@@ -3722,7 +3722,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.52696183746906</v>
+        <v>18.22516438163779</v>
       </c>
       <c r="D12" t="n">
         <v>20.17786056538469</v>
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>12.74799393964483</v>
       </c>
       <c r="D13" t="n">
         <v>16.1301147807751</v>
@@ -3753,7 +3753,7 @@
         <v>11.36962016288231</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>10.75504610002381</v>
       </c>
     </row>
     <row r="15">
@@ -3767,7 +3767,7 @@
         <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>6.091744504851459</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>2.89321048441535</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.91561075516378</v>
+        <v>8.083710596768237</v>
       </c>
       <c r="C2" t="n">
-        <v>9.127308406382596</v>
+        <v>8.486227155509429</v>
       </c>
       <c r="D2" t="n">
-        <v>11.28911685113407</v>
+        <v>19.9451863594782</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.21031499288707</v>
+        <v>2.915790681613027</v>
       </c>
       <c r="C2" t="n">
-        <v>3.729659528433633</v>
+        <v>6.444191930676063</v>
       </c>
       <c r="D2" t="n">
-        <v>7.252170291271189</v>
+        <v>15.67163860289183</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.52281386247382</v>
+        <v>17.0971362694582</v>
       </c>
       <c r="C3" t="n">
-        <v>24.78422079371073</v>
+        <v>27.98471830955533</v>
       </c>
       <c r="D3" t="n">
-        <v>68.66343443502193</v>
+        <v>96.03946916794422</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>47.553895298307</v>
+        <v>49.53211692236432</v>
       </c>
       <c r="C4" t="n">
-        <v>91.30449999036186</v>
+        <v>93.29548433457438</v>
       </c>
       <c r="D4" t="n">
-        <v>165.302751450261</v>
+        <v>216.3536320710951</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.61918936840603</v>
+        <v>36.32466505713199</v>
       </c>
       <c r="C5" t="n">
-        <v>234.5149828519569</v>
+        <v>246.1977805324939</v>
       </c>
       <c r="D5" t="n">
-        <v>152.0481756952248</v>
+        <v>203.6144738607885</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>18.67676832559133</v>
+        <v>19.24029150782899</v>
       </c>
       <c r="C6" t="n">
-        <v>275.482332802472</v>
+        <v>263.6885976313551</v>
       </c>
       <c r="D6" t="n">
-        <v>79.85928525425255</v>
+        <v>99.09957676208155</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.270021676396877</v>
+        <v>5.509568116233099</v>
       </c>
       <c r="C7" t="n">
-        <v>193.7930698275034</v>
+        <v>164.8678372172796</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>33.17718191731671</v>
       </c>
     </row>
     <row r="8">
@@ -4288,10 +4288,10 @@
         <v>1.585522542358599</v>
       </c>
       <c r="C8" t="n">
-        <v>102.725171033865</v>
+        <v>80.44440688598364</v>
       </c>
       <c r="D8" t="n">
-        <v>24.45042657426681</v>
+        <v>23.94973524510094</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3328124717396686</v>
+        <v>0.2218749811597791</v>
       </c>
       <c r="C9" t="n">
-        <v>38.93905919354123</v>
+        <v>32.61562223048752</v>
       </c>
       <c r="D9" t="n">
-        <v>20.1906232855399</v>
+        <v>19.52499834206056</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>21.49536598448391</v>
+        <v>19.78712497909446</v>
       </c>
       <c r="D10" t="n">
-        <v>19.21771131063132</v>
+        <v>18.64829764216817</v>
       </c>
     </row>
     <row r="11">
@@ -4330,7 +4330,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.63727743324319</v>
+        <v>14.57109942643116</v>
       </c>
       <c r="D11" t="n">
         <v>16.17036643664921</v>
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.63134588928871</v>
+        <v>10.41437964665016</v>
       </c>
       <c r="D12" t="n">
         <v>13.0179745583127</v>
@@ -4361,7 +4361,7 @@
         <v>9.365873098514571</v>
       </c>
       <c r="D13" t="n">
-        <v>9.365873098514571</v>
+        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -4375,7 +4375,7 @@
         <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>4.916592502868027</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.57528845915541</v>
+        <v>21.85861263505523</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>2.150027472300515</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.000441968356505</v>
+        <v>7.440665850486575</v>
       </c>
       <c r="C2" t="n">
-        <v>4.633849164044945</v>
+        <v>5.213080309550564</v>
       </c>
       <c r="D2" t="n">
-        <v>16.5748464907989</v>
+        <v>32.76975662005428</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.44579557318606</v>
+        <v>17.16094987023424</v>
       </c>
       <c r="C3" t="n">
-        <v>22.99743997198154</v>
+        <v>21.38246499849553</v>
       </c>
       <c r="D3" t="n">
-        <v>12.62036673809275</v>
+        <v>19.89020848804038</v>
       </c>
     </row>
     <row r="4">
@@ -4557,7 +4557,7 @@
         <v>4.736932672990861</v>
       </c>
       <c r="C5" t="n">
-        <v>9.35114688295087</v>
+        <v>9.449321653375552</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4571,7 +4571,7 @@
         <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>18.43525839034661</v>
       </c>
       <c r="D6" t="n">
         <v>32.8453511932813</v>
@@ -4585,7 +4585,7 @@
         <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>20.72076704583318</v>
       </c>
       <c r="D7" t="n">
         <v>32.21899615797182</v>
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>8.845546815263761</v>
       </c>
       <c r="C8" t="n">
         <v>21.69662426385451</v>
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>8.764061755811273</v>
       </c>
       <c r="C9" t="n">
         <v>22.74218556887735</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>39.60468413702056</v>
       </c>
     </row>
     <row r="10">
@@ -4630,7 +4630,7 @@
         <v>25.62361508084176</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>50.1084028247572</v>
       </c>
     </row>
     <row r="11">
@@ -4638,7 +4638,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>6.930157044278233</v>
       </c>
       <c r="C11" t="n">
         <v>27.36523550817559</v>
@@ -4697,7 +4697,7 @@
         <v>5.375068680751286</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
         <v>42.28387362191012</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39765326020768</v>
+        <v>13.39573983238621</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14065530344023</v>
+        <v>70.13063794602191</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576194501200904</v>
+        <v>1.575969392045436</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.685881792370026</v>
+        <v>6.42652047199962</v>
       </c>
       <c r="C2" t="n">
-        <v>10.46248528415826</v>
+        <v>5.124723016168351</v>
       </c>
       <c r="D2" t="n">
-        <v>16.50906939461436</v>
+        <v>41.68304402691108</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.60135367881356</v>
+        <v>22.48693116577319</v>
       </c>
       <c r="C3" t="n">
-        <v>19.91475218064655</v>
+        <v>20.72469403665017</v>
       </c>
       <c r="D3" t="n">
-        <v>23.49322256262617</v>
+        <v>42.7992911666397</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>12.22668590868978</v>
+        <v>19.4376227963826</v>
       </c>
       <c r="C4" t="n">
-        <v>35.5952265128766</v>
+        <v>33.13202152292136</v>
       </c>
       <c r="D4" t="n">
-        <v>21.6838615436993</v>
+        <v>25.00216878405352</v>
       </c>
     </row>
     <row r="5">
@@ -4865,10 +4865,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>3.117048960983624</v>
       </c>
       <c r="C5" t="n">
-        <v>5.375068680751288</v>
+        <v>5.522330836388309</v>
       </c>
       <c r="D5" t="n">
         <v>29.40334374219198</v>
@@ -4879,10 +4879,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>7.366053024963819</v>
       </c>
       <c r="C6" t="n">
-        <v>16.50317890838889</v>
+        <v>16.58368222013712</v>
       </c>
       <c r="D6" t="n">
         <v>34.57617239586842</v>
@@ -4893,10 +4893,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>24.3139636433765</v>
       </c>
       <c r="D7" t="n">
         <v>34.97378021608837</v>
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>9.513135254151592</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>25.20146356801562</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>36.96770980341364</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>9.429686699290611</v>
       </c>
       <c r="C9" t="n">
         <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>40.04843409934012</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>8.825911861178826</v>
       </c>
       <c r="C10" t="n">
         <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>49.68134257340984</v>
       </c>
     </row>
     <row r="11">
@@ -4952,7 +4952,7 @@
         <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
         <v>47.97801030654161</v>
@@ -4963,10 +4963,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>6.292021036517808</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>29.07347651356504</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -4980,7 +4980,7 @@
         <v>5.203262832508096</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>26.53664044579129</v>
       </c>
       <c r="D13" t="n">
         <v>44.74806035956962</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5025,7 +5025,7 @@
         <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>36.36098972218912</v>
       </c>
     </row>
     <row r="18">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43990574113356</v>
+        <v>15.43205587665261</v>
       </c>
       <c r="C21" t="n">
-        <v>86.13842150316619</v>
+        <v>86.09462752237772</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250506471817592</v>
+        <v>3.248853868768971</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.842961425049515</v>
+        <v>5.625414345334224</v>
       </c>
       <c r="C2" t="n">
-        <v>6.547275439621979</v>
+        <v>6.828055283036567</v>
       </c>
       <c r="D2" t="n">
-        <v>20.81599657314512</v>
+        <v>41.37772049089032</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.39518666092173</v>
+        <v>22.3003991019663</v>
       </c>
       <c r="C3" t="n">
-        <v>32.52530144169683</v>
+        <v>20.24363766156923</v>
       </c>
       <c r="D3" t="n">
-        <v>31.24902942617598</v>
+        <v>66.62630794870978</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.53445596620454</v>
+        <v>32.85124167950677</v>
       </c>
       <c r="C4" t="n">
-        <v>44.01862181531424</v>
+        <v>43.99309637500382</v>
       </c>
       <c r="D4" t="n">
-        <v>28.58849314766712</v>
+        <v>39.73034784316418</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>10.92194320974577</v>
+        <v>16.22338081267855</v>
       </c>
       <c r="C5" t="n">
-        <v>39.76078202199582</v>
+        <v>36.66827675361837</v>
       </c>
       <c r="D5" t="n">
-        <v>30.4587225242573</v>
+        <v>31.90680038802134</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>5.997496725243765</v>
       </c>
       <c r="C6" t="n">
-        <v>12.23650338573225</v>
+        <v>12.47801332097696</v>
       </c>
       <c r="D6" t="n">
-        <v>36.54850353370026</v>
+        <v>36.10573531908495</v>
       </c>
     </row>
     <row r="7">
@@ -5207,7 +5207,7 @@
         <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.25407703341745</v>
+        <v>24.19419042345839</v>
       </c>
       <c r="D7" t="n">
         <v>37.4890178343687</v>
@@ -5221,10 +5221,10 @@
         <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>29.45733986592554</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>38.13598957146735</v>
       </c>
     </row>
     <row r="9">
@@ -5235,10 +5235,10 @@
         <v>9.984374152190059</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>29.39843500367073</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>41.04687151455913</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.537678946757763</v>
+        <v>9.395325529641976</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>29.60951076008381</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>49.39663573917827</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>8.174031385558941</v>
       </c>
       <c r="C11" t="n">
-        <v>30.91916219754903</v>
+        <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>49.04418831335365</v>
       </c>
     </row>
     <row r="12">
@@ -5291,7 +5291,7 @@
         <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>29.91876128692155</v>
       </c>
       <c r="D13" t="n">
         <v>45.00822350119503</v>
@@ -5305,7 +5305,7 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>27.3485457972034</v>
       </c>
       <c r="D14" t="n">
         <v>45.47848065152925</v>
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>27.23368131580652</v>
+        <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>43.71722527011046</v>
       </c>
     </row>
     <row r="16">
@@ -5350,7 +5350,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73222303359087</v>
+        <v>16.71314854493277</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0665605049043</v>
+        <v>101.1145486968432</v>
       </c>
       <c r="D21" t="n">
-        <v>5.019666910077262</v>
+        <v>4.178287136233192</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.606180301876787</v>
+        <v>7.085273181549231</v>
       </c>
       <c r="C2" t="n">
-        <v>9.904852588146069</v>
+        <v>12.10593094106742</v>
       </c>
       <c r="D2" t="n">
-        <v>20.41446176210817</v>
+        <v>42.91906438655781</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.64553232550467</v>
+        <v>20.57252314249191</v>
       </c>
       <c r="C3" t="n">
-        <v>28.40196108386023</v>
+        <v>23.6846633649543</v>
       </c>
       <c r="D3" t="n">
-        <v>40.11911993404591</v>
+        <v>82.23609644623407</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.73339089726815</v>
+        <v>37.89251614081414</v>
       </c>
       <c r="C4" t="n">
-        <v>64.89843198923539</v>
+        <v>47.13272553318512</v>
       </c>
       <c r="D4" t="n">
-        <v>37.31819373382976</v>
+        <v>61.19724314422493</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>22.99743997198154</v>
+        <v>32.37313054753858</v>
       </c>
       <c r="C5" t="n">
-        <v>62.19371706403545</v>
+        <v>60.27930904075417</v>
       </c>
       <c r="D5" t="n">
-        <v>33.45305302221007</v>
+        <v>38.60722846950583</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.465430527271</v>
+        <v>13.56480802957818</v>
       </c>
       <c r="C6" t="n">
-        <v>38.40007970390975</v>
+        <v>35.66296710446964</v>
       </c>
       <c r="D6" t="n">
-        <v>38.35982804803563</v>
+        <v>37.8768081775462</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.563785224144926</v>
+        <v>8.623671834103982</v>
       </c>
       <c r="C7" t="n">
         <v>21.19985992550562</v>
       </c>
       <c r="D7" t="n">
-        <v>39.52516257297658</v>
+        <v>39.76470901281281</v>
       </c>
     </row>
     <row r="8">
@@ -5532,10 +5532,10 @@
         <v>10.84831213192725</v>
       </c>
       <c r="C8" t="n">
-        <v>31.71045084717197</v>
+        <v>31.37665662772806</v>
       </c>
       <c r="D8" t="n">
-        <v>39.8884092235479</v>
+        <v>39.55461500410399</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>10.6499990956694</v>
       </c>
       <c r="C9" t="n">
-        <v>33.9468721174462</v>
+        <v>33.39218466454675</v>
       </c>
       <c r="D9" t="n">
-        <v>42.15624642035802</v>
+        <v>42.04530892977813</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10.10709261522091</v>
+        <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.59540643932586</v>
+        <v>33.16834618797849</v>
       </c>
       <c r="D10" t="n">
-        <v>48.68486865359933</v>
+        <v>48.82722207071512</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>8.707120388964958</v>
       </c>
       <c r="C11" t="n">
         <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>50.28806265463436</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>7.159886007071988</v>
       </c>
       <c r="C12" t="n">
-        <v>33.84673385161303</v>
+        <v>34.06370009425158</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>47.51560713784138</v>
       </c>
     </row>
     <row r="13">
@@ -5602,10 +5602,10 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>33.04071898642641</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="14">
@@ -5616,10 +5616,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.11412908006666</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>45.7857676829585</v>
       </c>
     </row>
     <row r="15">
@@ -5644,7 +5644,7 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
         <v>41.33157834879071</v>
@@ -5661,7 +5661,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5689,7 +5689,7 @@
         <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>25.27607639353838</v>
       </c>
     </row>
     <row r="20">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.05543636235683</v>
+        <v>18.02076458118837</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7902276972803</v>
+        <v>116.7059039543628</v>
       </c>
       <c r="D21" t="n">
-        <v>6.878261471374032</v>
+        <v>6.006921527062791</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.58105577219387</v>
+        <v>6.816274310585604</v>
       </c>
       <c r="C2" t="n">
-        <v>6.58065486156637</v>
+        <v>6.773077411598745</v>
       </c>
       <c r="D2" t="n">
-        <v>33.7495408288926</v>
+        <v>37.15816885803753</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.82362957060084</v>
+        <v>19.89511722656161</v>
       </c>
       <c r="C3" t="n">
-        <v>32.10805866739193</v>
+        <v>34.27281235525615</v>
       </c>
       <c r="D3" t="n">
-        <v>43.94302724208723</v>
+        <v>89.87900232379549</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.04121770804514</v>
+        <v>27.86101809882023</v>
       </c>
       <c r="C4" t="n">
-        <v>57.18974901548945</v>
+        <v>44.78438502462675</v>
       </c>
       <c r="D4" t="n">
-        <v>42.21907827342983</v>
+        <v>74.20245498238242</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>19.65949777754238</v>
+        <v>26.94897448157495</v>
       </c>
       <c r="C5" t="n">
-        <v>69.18866945679397</v>
+        <v>54.51154127830416</v>
       </c>
       <c r="D5" t="n">
-        <v>31.3668391506856</v>
+        <v>41.35612204139689</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.3107153006275</v>
+        <v>15.41638419978766</v>
       </c>
       <c r="C6" t="n">
-        <v>46.77242412572655</v>
+        <v>44.59883470852411</v>
       </c>
       <c r="D6" t="n">
-        <v>31.31578827006476</v>
+        <v>31.63780151705772</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.329908286355933</v>
+        <v>6.048547605864599</v>
       </c>
       <c r="C7" t="n">
-        <v>24.73316991308989</v>
+        <v>22.93657161431823</v>
       </c>
       <c r="D7" t="n">
-        <v>30.78171751895449</v>
+        <v>31.14103717870882</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>18.60902773399829</v>
       </c>
       <c r="D8" t="n">
-        <v>30.0414797499524</v>
+        <v>29.45733986592554</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>22.07656062539802</v>
+        <v>21.41093568191868</v>
       </c>
       <c r="D9" t="n">
-        <v>29.95312245657017</v>
+        <v>30.17499743772996</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>21.06830573313655</v>
       </c>
       <c r="D10" t="n">
-        <v>33.45305302221006</v>
+        <v>33.16834618797849</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>3.553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>20.43507846389736</v>
+        <v>20.07968579496001</v>
       </c>
       <c r="D11" t="n">
-        <v>34.65078522139116</v>
+        <v>34.47308888692249</v>
       </c>
     </row>
     <row r="12">
@@ -5896,7 +5896,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>2.820561154301086</v>
       </c>
       <c r="C12" t="n">
         <v>19.7439280801076</v>
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>2.081305133003238</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>18.73174619702914</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>30.17892442854696</v>
       </c>
     </row>
     <row r="14">
@@ -5927,10 +5927,10 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -5944,7 +5944,7 @@
         <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>27.95035713990669</v>
       </c>
     </row>
     <row r="16">
@@ -5958,7 +5958,7 @@
         <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -5969,10 +5969,10 @@
         <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>23.13881164139307</v>
       </c>
     </row>
     <row r="18">
@@ -5980,10 +5980,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>17.12167996206437</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.055191967967714</v>
+        <v>7.035035002040011</v>
       </c>
       <c r="C21" t="n">
-        <v>66.14242469969732</v>
+        <v>65.95345314412511</v>
       </c>
       <c r="D21" t="n">
-        <v>5.291393975975785</v>
+        <v>4.396896876275007</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.517422097867075</v>
+        <v>5.913066422678538</v>
       </c>
       <c r="C2" t="n">
-        <v>5.175773896789184</v>
+        <v>7.200137662946108</v>
       </c>
       <c r="D2" t="n">
-        <v>39.91589815926682</v>
+        <v>35.5196319396496</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.05634483423634</v>
+        <v>22.20713307006285</v>
       </c>
       <c r="C3" t="n">
-        <v>27.98471830955533</v>
+        <v>29.35425635697963</v>
       </c>
       <c r="D3" t="n">
-        <v>61.67339078078462</v>
+        <v>99.37250262386215</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.72437524148068</v>
+        <v>34.57420890045992</v>
       </c>
       <c r="C4" t="n">
-        <v>71.89240263428968</v>
+        <v>69.79931652883548</v>
       </c>
       <c r="D4" t="n">
-        <v>55.04561202941441</v>
+        <v>104.0927455858808</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.66074156715389</v>
+        <v>35.29382996767284</v>
       </c>
       <c r="C5" t="n">
-        <v>91.62160449883359</v>
+        <v>71.27488332831845</v>
       </c>
       <c r="D5" t="n">
-        <v>40.44800541496859</v>
+        <v>59.54299826256906</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>20.12582793705961</v>
+        <v>27.29062268265284</v>
       </c>
       <c r="C6" t="n">
-        <v>83.96495415341272</v>
+        <v>68.54856995362505</v>
       </c>
       <c r="D6" t="n">
-        <v>34.69692736349078</v>
+        <v>37.47429161880501</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.941177253203202</v>
+        <v>12.87562114119692</v>
       </c>
       <c r="C7" t="n">
-        <v>49.76577287597506</v>
+        <v>46.05280305851362</v>
       </c>
       <c r="D7" t="n">
-        <v>33.0574086973986</v>
+        <v>33.77604801690726</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.591053175685585</v>
+        <v>5.9248473951295</v>
       </c>
       <c r="C8" t="n">
-        <v>27.03733177495716</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>32.12769362147687</v>
+        <v>31.54355373745002</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>23.2968730217768</v>
+        <v>23.07499804061703</v>
       </c>
       <c r="D9" t="n">
-        <v>31.39530983410874</v>
+        <v>31.06249736236907</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.48478774391545</v>
+        <v>24.05772749256809</v>
       </c>
       <c r="D10" t="n">
-        <v>33.59540643932586</v>
+        <v>33.73775985644164</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>3.909319358310797</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>34.82848155585983</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>21.47965802121596</v>
       </c>
       <c r="D12" t="n">
-        <v>33.1958351236974</v>
+        <v>32.97886888105885</v>
       </c>
     </row>
     <row r="13">
@@ -6221,10 +6221,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>21.07321447165778</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
         <v>30.95941385342317</v>
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>19.0517959486136</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -6252,10 +6252,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.20021977840412</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -6280,10 +6280,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>23.13881164139307</v>
       </c>
     </row>
     <row r="18">
@@ -6294,10 +6294,10 @@
         <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>17.12167996206437</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6305,7 +6305,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>1.203622685406589</v>
       </c>
       <c r="C19" t="n">
         <v>18.65615162380213</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.274655928272466</v>
+        <v>7.247113586363468</v>
       </c>
       <c r="C21" t="n">
-        <v>75.47455525582684</v>
+        <v>75.18880345852098</v>
       </c>
       <c r="D21" t="n">
-        <v>6.365323937238408</v>
+        <v>5.435335189772601</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.396667130244716</v>
+        <v>4.851797154387737</v>
       </c>
       <c r="C2" t="n">
-        <v>7.453428570641783</v>
+        <v>6.989061906533043</v>
       </c>
       <c r="D2" t="n">
-        <v>29.98061139228909</v>
+        <v>33.63565809519997</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.80814259151115</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="C3" t="n">
-        <v>23.28705554473434</v>
+        <v>28.52467954689108</v>
       </c>
       <c r="D3" t="n">
-        <v>79.29576207201488</v>
+        <v>104.2665149295325</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.93080430127976</v>
+        <v>39.3219407981975</v>
       </c>
       <c r="C4" t="n">
-        <v>70.871385021873</v>
+        <v>71.84135175366885</v>
       </c>
       <c r="D4" t="n">
-        <v>73.5898444149324</v>
+        <v>129.0566262094687</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.93825737228624</v>
+        <v>43.73686022419541</v>
       </c>
       <c r="C5" t="n">
-        <v>114.7663066264522</v>
+        <v>101.7336058525757</v>
       </c>
       <c r="D5" t="n">
-        <v>51.12451169865266</v>
+        <v>81.4605157598791</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.26295382048468</v>
+        <v>38.11831811279092</v>
       </c>
       <c r="C6" t="n">
-        <v>116.5285437555752</v>
+        <v>92.37755023110364</v>
       </c>
       <c r="D6" t="n">
-        <v>39.32586778901449</v>
+        <v>47.33594730796422</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.48689010804419</v>
+        <v>22.75691178444107</v>
       </c>
       <c r="C7" t="n">
-        <v>88.75195595932016</v>
+        <v>73.95996329943345</v>
       </c>
       <c r="D7" t="n">
-        <v>35.99185258539232</v>
+        <v>36.71049190490098</v>
       </c>
     </row>
     <row r="8">
@@ -6462,10 +6462,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.344855486097888</v>
+        <v>10.09727513817844</v>
       </c>
       <c r="C8" t="n">
-        <v>48.14981615478482</v>
+        <v>43.81049130201391</v>
       </c>
       <c r="D8" t="n">
         <v>33.79666471869644</v>
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>29.28749751309084</v>
+        <v>28.17812260729194</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>32.06093477758807</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>26.62008900065227</v>
+        <v>26.47773558353648</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>34.30717352490479</v>
       </c>
     </row>
     <row r="11">
@@ -6504,10 +6504,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.264712027248144</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>25.58827216348886</v>
       </c>
       <c r="D11" t="n">
         <v>35.53926689373453</v>
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>24.0832529328785</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>33.41280136633594</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>22.63419332141022</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>31.73990327829938</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>21.20280516861837</v>
+        <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -6577,10 +6577,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>17.3592629064921</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -6594,7 +6594,7 @@
         <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>23.13881164139307</v>
       </c>
     </row>
     <row r="18">
@@ -6608,7 +6608,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
         <v>18.82992096745382</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.479371342105653</v>
+        <v>7.444550373376908</v>
       </c>
       <c r="C21" t="n">
-        <v>84.14292759868859</v>
+        <v>83.75119170049021</v>
       </c>
       <c r="D21" t="n">
-        <v>7.479371342105653</v>
+        <v>6.513981576704794</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_16_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_16_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497613882621</v>
+        <v>10.84497631846007</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907126805048</v>
+        <v>37.78907189398055</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.094689747964199</v>
+        <v>3.474405125329462</v>
       </c>
       <c r="C2" t="n">
-        <v>12.19625172985812</v>
+        <v>8.939794594871456</v>
       </c>
       <c r="D2" t="n">
-        <v>34.39847606139974</v>
+        <v>30.05915120862884</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.60902773399829</v>
+        <v>14.93729132011522</v>
       </c>
       <c r="C3" t="n">
-        <v>27.67546778271759</v>
+        <v>28.51486206984861</v>
       </c>
       <c r="D3" t="n">
-        <v>105.9502122423158</v>
+        <v>69.93479771202153</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.89626320518188</v>
+        <v>32.48112279500572</v>
       </c>
       <c r="C4" t="n">
-        <v>70.78204598078653</v>
+        <v>77.87811838708248</v>
       </c>
       <c r="D4" t="n">
-        <v>147.0648243484679</v>
+        <v>91.62356799424208</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.65818153913543</v>
+        <v>38.43542262126263</v>
       </c>
       <c r="C5" t="n">
-        <v>117.0979574240383</v>
+        <v>135.7266201121216</v>
       </c>
       <c r="D5" t="n">
-        <v>106.1760142142926</v>
+        <v>70.17041716104079</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>47.97997380195012</v>
+        <v>33.56988099901544</v>
       </c>
       <c r="C6" t="n">
-        <v>124.8606365215179</v>
+        <v>139.1902260127043</v>
       </c>
       <c r="D6" t="n">
-        <v>59.4516957260741</v>
+        <v>48.5434969841878</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>33.65627479698915</v>
+        <v>23.35577788403162</v>
       </c>
       <c r="C7" t="n">
-        <v>103.1247423494934</v>
+        <v>101.9868967602714</v>
       </c>
       <c r="D7" t="n">
-        <v>41.62119392154352</v>
+        <v>39.88448223273092</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>16.77315952705676</v>
+        <v>12.68418033886879</v>
       </c>
       <c r="C8" t="n">
-        <v>69.42919764433444</v>
+        <v>62.83676181031709</v>
       </c>
       <c r="D8" t="n">
-        <v>35.63253292563798</v>
+        <v>36.30012136452581</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.876561831172157</v>
+        <v>6.878124415953151</v>
       </c>
       <c r="C9" t="n">
-        <v>41.04687151455913</v>
+        <v>37.05312185368311</v>
       </c>
       <c r="D9" t="n">
-        <v>33.61405964570653</v>
+        <v>34.39062207976576</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.551783267515713</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>30.17892442854695</v>
+        <v>30.03657101143117</v>
       </c>
       <c r="D10" t="n">
-        <v>34.44952694202058</v>
+        <v>35.01894061048373</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>28.43141351498762</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>26.68684784454105</v>
+        <v>27.55471281509523</v>
       </c>
       <c r="D12" t="n">
-        <v>33.84673385161303</v>
+        <v>34.93156506480576</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>24.45533531278805</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>32.26022956155019</v>
+        <v>32.00006641992479</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>22.73924032576462</v>
+        <v>23.66110142005238</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -962,13 +962,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -979,7 +979,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>18.59921025695582</v>
+        <v>19.42584182393164</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -993,10 +993,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
-        <v>23.13881164139307</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1007,7 +1007,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -1024,7 +1024,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.626667730977979</v>
+        <v>7.691637233086565</v>
       </c>
       <c r="C21" t="n">
-        <v>91.52001277173574</v>
+        <v>94.22255610531042</v>
       </c>
       <c r="D21" t="n">
-        <v>7.626667730977979</v>
+        <v>8.653091887222386</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.015970005175207</v>
+        <v>4.319689898685966</v>
       </c>
       <c r="C2" t="n">
-        <v>7.826492698255572</v>
+        <v>8.084692344472483</v>
       </c>
       <c r="D2" t="n">
-        <v>28.90363416073034</v>
+        <v>33.43930855435061</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.17844140246144</v>
+        <v>13.2045066221196</v>
       </c>
       <c r="C3" t="n">
-        <v>37.00697971158352</v>
+        <v>31.56318869153495</v>
       </c>
       <c r="D3" t="n">
-        <v>107.4522862298134</v>
+        <v>76.16398689546754</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.13951565165684</v>
+        <v>30.15830772675777</v>
       </c>
       <c r="C4" t="n">
-        <v>69.8376046893011</v>
+        <v>74.4577093854866</v>
       </c>
       <c r="D4" t="n">
-        <v>162.3162749339421</v>
+        <v>103.5567113393621</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>54.78152189697203</v>
+        <v>42.92691836819179</v>
       </c>
       <c r="C5" t="n">
-        <v>121.7367153266045</v>
+        <v>138.0582709097077</v>
       </c>
       <c r="D5" t="n">
-        <v>127.3572209334175</v>
+        <v>83.64490440182826</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>56.43282153551517</v>
+        <v>42.22398701195107</v>
       </c>
       <c r="C6" t="n">
-        <v>150.8632062161989</v>
+        <v>175.4167162994116</v>
       </c>
       <c r="D6" t="n">
-        <v>75.14984151698062</v>
+        <v>58.08313942635406</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>43.59745205019235</v>
+        <v>30.84160412891355</v>
       </c>
       <c r="C7" t="n">
-        <v>137.8589761257456</v>
+        <v>147.2611738893173</v>
       </c>
       <c r="D7" t="n">
-        <v>47.19064864773568</v>
+        <v>43.83699849002857</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>25.03456645829366</v>
+        <v>18.44213062427633</v>
       </c>
       <c r="C8" t="n">
-        <v>98.55274329081605</v>
+        <v>96.96722074845746</v>
       </c>
       <c r="D8" t="n">
-        <v>38.30288668118931</v>
+        <v>38.7201294554942</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>11.6484365108884</v>
+        <v>9.540624189870499</v>
       </c>
       <c r="C9" t="n">
-        <v>61.01561981893925</v>
+        <v>55.80155776168444</v>
       </c>
       <c r="D9" t="n">
-        <v>34.61249706092553</v>
+        <v>35.49999698556465</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.548257187326225</v>
+        <v>6.121196935978863</v>
       </c>
       <c r="C10" t="n">
-        <v>38.15071578703105</v>
+        <v>37.01188845010476</v>
       </c>
       <c r="D10" t="n">
-        <v>35.16129402759952</v>
+        <v>35.87306111317846</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>32.16303653882975</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>36.42774856607789</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>29.50740899884213</v>
+        <v>30.59224021203486</v>
       </c>
       <c r="D12" t="n">
-        <v>34.49763257952867</v>
+        <v>35.58246379272139</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>26.53664044579129</v>
+        <v>27.83745615391831</v>
       </c>
       <c r="D13" t="n">
-        <v>32.26022956155019</v>
+        <v>32.5203927031756</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>24.58296251434014</v>
+        <v>25.81211064005714</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>31.34327720578367</v>
       </c>
     </row>
     <row r="15">
@@ -1273,13 +1273,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.85861263505523</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -1287,10 +1287,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.8266315669758143</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.83915760741954</v>
+        <v>20.66578917439536</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -1304,10 +1304,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
-        <v>23.13881164139307</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1318,7 +1318,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -1335,7 +1335,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.792835434129308</v>
+        <v>7.870803157930674</v>
       </c>
       <c r="C21" t="n">
-        <v>99.35865178514868</v>
+        <v>102.3204410530988</v>
       </c>
       <c r="D21" t="n">
-        <v>8.766939863395471</v>
+        <v>9.838503947413344</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.619164006210248</v>
+        <v>5.778566987196725</v>
       </c>
       <c r="C2" t="n">
-        <v>7.992408060273283</v>
+        <v>12.96496018228338</v>
       </c>
       <c r="D2" t="n">
-        <v>42.80910864368217</v>
+        <v>31.63092928312799</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.8389776809703</v>
+        <v>13.53830084156352</v>
       </c>
       <c r="C3" t="n">
-        <v>34.06664533736432</v>
+        <v>31.21466825652734</v>
       </c>
       <c r="D3" t="n">
-        <v>106.0532957512617</v>
+        <v>82.2115527536279</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.7483791547391</v>
+        <v>27.55471281509523</v>
       </c>
       <c r="C4" t="n">
-        <v>78.3503390328252</v>
+        <v>75.47872699790328</v>
       </c>
       <c r="D4" t="n">
-        <v>171.5437216061579</v>
+        <v>113.0138869743716</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>54.58517235612267</v>
+        <v>43.56505437595222</v>
       </c>
       <c r="C5" t="n">
-        <v>122.963899956913</v>
+        <v>137.3465038241288</v>
       </c>
       <c r="D5" t="n">
-        <v>147.0903497887784</v>
+        <v>97.73298395777</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>62.83283481950012</v>
+        <v>48.50324532831367</v>
       </c>
       <c r="C6" t="n">
-        <v>166.8431135982242</v>
+        <v>192.6846766694088</v>
       </c>
       <c r="D6" t="n">
-        <v>92.13604029585892</v>
+        <v>67.3812719332756</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>52.58044354405067</v>
+        <v>38.80652325346792</v>
       </c>
       <c r="C7" t="n">
-        <v>170.8564982131851</v>
+        <v>191.3976054291412</v>
       </c>
       <c r="D7" t="n">
-        <v>54.43692845278139</v>
+        <v>49.22679338634357</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>33.54631905411351</v>
+        <v>24.61732368398877</v>
       </c>
       <c r="C8" t="n">
-        <v>131.4314739060417</v>
+        <v>139.2756380629737</v>
       </c>
       <c r="D8" t="n">
-        <v>41.39048321104552</v>
+        <v>40.72289477215769</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16.86249856814321</v>
+        <v>13.31249886958674</v>
       </c>
       <c r="C9" t="n">
-        <v>85.08905527477528</v>
+        <v>82.42655550085793</v>
       </c>
       <c r="D9" t="n">
-        <v>35.83280945730432</v>
+        <v>36.72030938194344</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.398851609831464</v>
+        <v>7.402377690020952</v>
       </c>
       <c r="C10" t="n">
-        <v>51.38958357879929</v>
+        <v>49.11192890494669</v>
       </c>
       <c r="D10" t="n">
-        <v>35.87306111317846</v>
+        <v>36.72718161587318</v>
       </c>
     </row>
     <row r="11">
@@ -1531,10 +1531,10 @@
         <v>5.153193699591506</v>
       </c>
       <c r="C11" t="n">
-        <v>36.78314123501524</v>
+        <v>36.96083756948391</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>36.60544490054656</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>31.89403766786613</v>
+        <v>32.97886888105885</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>36.23336252063703</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>28.87810872041993</v>
+        <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
-        <v>32.26022956155019</v>
+        <v>32.780555844801</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>26.42668470291564</v>
+        <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>31.65056423721292</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>24.72531593145592</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -1598,10 +1598,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.8266315669758143</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.66578917439536</v>
+        <v>21.90573652485908</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>19.83326712119407</v>
       </c>
       <c r="D17" t="n">
-        <v>23.13881164139307</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1629,7 +1629,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -1646,7 +1646,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.943568409209668</v>
+        <v>8.033640911805669</v>
       </c>
       <c r="C21" t="n">
-        <v>106.2452274731793</v>
+        <v>110.462562537328</v>
       </c>
       <c r="D21" t="n">
-        <v>9.929460511512085</v>
+        <v>11.04625625373279</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.745408549430588</v>
+        <v>5.228788272818512</v>
       </c>
       <c r="C2" t="n">
-        <v>5.62639609303847</v>
+        <v>8.919177893082272</v>
       </c>
       <c r="D2" t="n">
-        <v>35.46858105902876</v>
+        <v>26.09387223117598</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.10819753611218</v>
+        <v>17.56346642897544</v>
       </c>
       <c r="C3" t="n">
-        <v>49.55371537185776</v>
+        <v>49.21010367537137</v>
       </c>
       <c r="D3" t="n">
-        <v>116.6021748333937</v>
+        <v>88.32784095108553</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.21462719879833</v>
+        <v>20.930861054542</v>
       </c>
       <c r="C4" t="n">
-        <v>102.7398972494287</v>
+        <v>109.8614950960351</v>
       </c>
       <c r="D4" t="n">
-        <v>163.9371403936536</v>
+        <v>108.8915283642392</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.39200473809752</v>
+        <v>27.3171298706675</v>
       </c>
       <c r="C5" t="n">
-        <v>99.69647936626362</v>
+        <v>115.1344620155447</v>
       </c>
       <c r="D5" t="n">
-        <v>93.16785713302231</v>
+        <v>66.51340696272142</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.6440929139107</v>
+        <v>24.0704902127233</v>
       </c>
       <c r="C6" t="n">
-        <v>112.5033781681633</v>
+        <v>126.0681861977414</v>
       </c>
       <c r="D6" t="n">
-        <v>35.82397372796611</v>
+        <v>32.40258297866598</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.21793229480956</v>
+        <v>16.28915790886308</v>
       </c>
       <c r="C7" t="n">
-        <v>92.40503916682252</v>
+        <v>97.91460728305563</v>
       </c>
       <c r="D7" t="n">
-        <v>29.10489244010094</v>
+        <v>28.62579956042849</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.68279768053704</v>
+        <v>9.179341034707678</v>
       </c>
       <c r="C8" t="n">
-        <v>62.66986470059513</v>
+        <v>60.75054793879262</v>
       </c>
       <c r="D8" t="n">
-        <v>26.36974333606933</v>
+        <v>27.03733177495716</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.990624491314035</v>
+        <v>5.324999547834698</v>
       </c>
       <c r="C9" t="n">
-        <v>39.160934174701</v>
+        <v>37.49687181600267</v>
       </c>
       <c r="D9" t="n">
-        <v>27.29062268265283</v>
+        <v>27.95624762613216</v>
       </c>
     </row>
     <row r="10">
@@ -1828,10 +1828,10 @@
         <v>3.701188845010476</v>
       </c>
       <c r="C10" t="n">
-        <v>28.75539025738908</v>
+        <v>28.89774367450487</v>
       </c>
       <c r="D10" t="n">
-        <v>28.18597658892593</v>
+        <v>28.61303684027329</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.843141351498762</v>
+        <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>25.58827216348886</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>28.07602084605028</v>
+        <v>28.96450251839364</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.952696183746906</v>
+        <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>23.43235420496287</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>26.25291535926396</v>
+        <v>26.68684784454105</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
-        <v>24.97566159603886</v>
+        <v>26.01631416254048</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.6145740628585034</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>20.58823110575986</v>
       </c>
       <c r="D14" t="n">
-        <v>24.58296251434014</v>
+        <v>23.66110142005238</v>
       </c>
     </row>
     <row r="15">
@@ -1895,10 +1895,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.3583379120500857</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>18.27523351455437</v>
       </c>
       <c r="D15" t="n">
         <v>22.57528845915541</v>
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.11931555602838</v>
+        <v>16.94594712300419</v>
       </c>
       <c r="D16" t="n">
-        <v>19.83915760741954</v>
+        <v>20.66578917439536</v>
       </c>
     </row>
     <row r="17">
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.11106066376691</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
         <v>17.47216389248049</v>
@@ -1943,7 +1943,7 @@
         <v>16.05157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>13.37631247036279</v>
+        <v>13.9113649691773</v>
       </c>
     </row>
     <row r="19">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
       <c r="D19" t="n">
         <v>9.027170140549421</v>
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>71.95719798276996</v>
+        <v>73.97468951499715</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>7.397468951499714</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.223879534297278</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C2" t="n">
-        <v>2.532909076956771</v>
+        <v>3.85041449605599</v>
       </c>
       <c r="D2" t="n">
-        <v>24.7626223442173</v>
+        <v>18.84170193990478</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>27.83745615391831</v>
+        <v>18.24087234490574</v>
       </c>
       <c r="C3" t="n">
-        <v>36.71245540030947</v>
+        <v>42.76002125846983</v>
       </c>
       <c r="D3" t="n">
-        <v>117.8440856792659</v>
+        <v>89.81518872301945</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.9953786655818</v>
+        <v>26.59750880345459</v>
       </c>
       <c r="C4" t="n">
-        <v>115.0814476395154</v>
+        <v>119.0634163279404</v>
       </c>
       <c r="D4" t="n">
-        <v>182.1495420551362</v>
+        <v>124.0153517481613</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.65631585471817</v>
+        <v>30.53235360207581</v>
       </c>
       <c r="C5" t="n">
-        <v>140.9298829446297</v>
+        <v>157.9386619207056</v>
       </c>
       <c r="D5" t="n">
-        <v>117.6870060465864</v>
+        <v>83.59581701661591</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.35982804803563</v>
+        <v>28.69943063824701</v>
       </c>
       <c r="C6" t="n">
-        <v>136.050596854523</v>
+        <v>155.4116433299744</v>
       </c>
       <c r="D6" t="n">
-        <v>46.53091419048183</v>
+        <v>40.29190752999335</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.54110721595601</v>
+        <v>15.4507453694363</v>
       </c>
       <c r="C7" t="n">
-        <v>117.9766216193392</v>
+        <v>129.2353042916416</v>
       </c>
       <c r="D7" t="n">
-        <v>32.03933632809466</v>
+        <v>31.32069700858599</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.680032363873551</v>
+        <v>7.927612711792993</v>
       </c>
       <c r="C8" t="n">
-        <v>82.28027509292518</v>
+        <v>82.6140693123691</v>
       </c>
       <c r="D8" t="n">
-        <v>26.95388322009618</v>
+        <v>28.28906009787184</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.548437113775471</v>
+        <v>4.437499623195581</v>
       </c>
       <c r="C9" t="n">
         <v>42.26718391093791</v>
       </c>
       <c r="D9" t="n">
-        <v>28.39999758845172</v>
+        <v>28.84374755077128</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.992947839621025</v>
+        <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>31.17539834835747</v>
+        <v>31.74481201682062</v>
       </c>
       <c r="D10" t="n">
-        <v>29.18245050873644</v>
+        <v>30.03657101143117</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.421570675749381</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>28.07602084605028</v>
+        <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
-        <v>28.96450251839364</v>
+        <v>29.67528785626833</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>19.52696183746906</v>
+        <v>21.26269177857742</v>
       </c>
       <c r="D12" t="n">
-        <v>27.55471281509523</v>
+        <v>28.42257778564941</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.2601631416254048</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>15.86995163914969</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>25.23582473766426</v>
       </c>
     </row>
     <row r="14">
@@ -2192,10 +2192,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>14.74977750860408</v>
+        <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
         <v>18.74450891718435</v>
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>14.33351648200343</v>
       </c>
       <c r="D15" t="n">
-        <v>16.84188186635403</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.81278928812512</v>
+        <v>13.63942085510094</v>
       </c>
       <c r="D16" t="n">
         <v>14.87936820556466</v>
@@ -2240,7 +2240,7 @@
         <v>13.69439872653876</v>
       </c>
       <c r="D17" t="n">
-        <v>11.33329549782518</v>
+        <v>11.8055161435679</v>
       </c>
     </row>
     <row r="18">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>13.9113649691773</v>
+        <v>14.44641746799181</v>
       </c>
       <c r="D18" t="n">
         <v>7.490734983403163</v>
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>62.58837964114266</v>
+        <v>64.39381366925254</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>6.018113427032947</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.378414834491527</v>
+        <v>3.02869166760141</v>
       </c>
       <c r="C2" t="n">
-        <v>7.102944640225672</v>
+        <v>5.85416156042373</v>
       </c>
       <c r="D2" t="n">
-        <v>25.40763058590745</v>
+        <v>23.97133369459437</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.03180114163017</v>
+        <v>14.5593184539802</v>
       </c>
       <c r="C3" t="n">
-        <v>22.93853510972673</v>
+        <v>27.96508335547039</v>
       </c>
       <c r="D3" t="n">
-        <v>111.8652421604028</v>
+        <v>84.37630644149212</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.83168884087984</v>
+        <v>30.60500293219007</v>
       </c>
       <c r="C4" t="n">
-        <v>103.4418468579652</v>
+        <v>112.7203444108018</v>
       </c>
       <c r="D4" t="n">
-        <v>193.9422954785489</v>
+        <v>138.1053947995115</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.76769531365456</v>
+        <v>34.87658719336795</v>
       </c>
       <c r="C5" t="n">
-        <v>175.6101205971482</v>
+        <v>189.5754816900591</v>
       </c>
       <c r="D5" t="n">
-        <v>149.8146996680633</v>
+        <v>104.8261111209532</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44.35732477327939</v>
+        <v>34.21390749300134</v>
       </c>
       <c r="C6" t="n">
-        <v>174.9336964289222</v>
+        <v>199.6482131356314</v>
       </c>
       <c r="D6" t="n">
-        <v>66.97875537453442</v>
+        <v>53.69570893607505</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>30.18285141936394</v>
+        <v>22.87668500435917</v>
       </c>
       <c r="C7" t="n">
-        <v>153.7888143748544</v>
+        <v>174.3898082007694</v>
       </c>
       <c r="D7" t="n">
-        <v>36.77037851486003</v>
+        <v>34.91389360612931</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.01935721664445</v>
+        <v>11.09865779651019</v>
       </c>
       <c r="C8" t="n">
-        <v>114.407968714402</v>
+        <v>122.502478535917</v>
       </c>
       <c r="D8" t="n">
-        <v>29.12354564648163</v>
+        <v>29.87458264023044</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.101561981893925</v>
+        <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>66.34061936677394</v>
+        <v>67.78280674431251</v>
       </c>
       <c r="D9" t="n">
-        <v>28.84374755077128</v>
+        <v>29.84218496599028</v>
       </c>
     </row>
     <row r="10">
@@ -2450,10 +2450,10 @@
         <v>2.562361508084175</v>
       </c>
       <c r="C10" t="n">
-        <v>39.14718970684157</v>
+        <v>40.00131020953629</v>
       </c>
       <c r="D10" t="n">
-        <v>29.75186417719959</v>
+        <v>30.32127784566274</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.421570675749381</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>31.62994753542373</v>
+        <v>32.87382187670443</v>
       </c>
       <c r="D11" t="n">
-        <v>29.49759152179966</v>
+        <v>30.20837685967435</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>23.64932044760141</v>
+        <v>25.60201663134832</v>
       </c>
       <c r="D12" t="n">
-        <v>27.98864530037232</v>
+        <v>28.8565102709265</v>
       </c>
     </row>
     <row r="13">
@@ -2489,10 +2489,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>17.69109363052753</v>
+        <v>19.25207248027995</v>
       </c>
       <c r="D13" t="n">
         <v>26.01631416254048</v>
@@ -2506,7 +2506,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>15.67163860289184</v>
+        <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
         <v>19.35908298004286</v>
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.40853021815369</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
-        <v>16.48354395430394</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="D16" t="n">
         <v>14.46605242207675</v>
@@ -2551,7 +2551,7 @@
         <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
-        <v>10.38885420633975</v>
+        <v>10.86107485208246</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>33.09962384868121</v>
+        <v>34.3032465340878</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>4.212679398923063</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.843542262126263</v>
+        <v>1.812306262039612</v>
       </c>
       <c r="C2" t="n">
-        <v>3.455751918948773</v>
+        <v>2.790126975469435</v>
       </c>
       <c r="D2" t="n">
-        <v>17.72741829558466</v>
+        <v>16.7132729170977</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.15590226299277</v>
+        <v>14.18134558784518</v>
       </c>
       <c r="C3" t="n">
-        <v>26.33538216642069</v>
+        <v>27.3171298706675</v>
       </c>
       <c r="D3" t="n">
-        <v>110.9325818413683</v>
+        <v>86.17290474026379</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>47.33692905566846</v>
+        <v>33.78292025083699</v>
       </c>
       <c r="C4" t="n">
-        <v>97.76243638889737</v>
+        <v>109.2105963681194</v>
       </c>
       <c r="D4" t="n">
-        <v>207.2155244399658</v>
+        <v>148.0730792407294</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.75573441475435</v>
+        <v>36.42283982755667</v>
       </c>
       <c r="C5" t="n">
-        <v>210.0694650162113</v>
+        <v>223.7403017978481</v>
       </c>
       <c r="D5" t="n">
-        <v>156.4660403643354</v>
+        <v>110.7902284242526</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.94472869558847</v>
+        <v>27.77364255314227</v>
       </c>
       <c r="C6" t="n">
-        <v>201.4595376499668</v>
+        <v>236.7199881956952</v>
       </c>
       <c r="D6" t="n">
-        <v>63.79887456047898</v>
+        <v>52.56866257159972</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.282424543653592</v>
+        <v>7.306166415004762</v>
       </c>
       <c r="C7" t="n">
-        <v>155.0464331839945</v>
+        <v>173.910715321097</v>
       </c>
       <c r="D7" t="n">
-        <v>35.99185258539232</v>
+        <v>34.85400699617026</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.172427743048944</v>
+        <v>3.922082078466008</v>
       </c>
       <c r="C8" t="n">
-        <v>81.36234098945441</v>
+        <v>87.12029127486194</v>
       </c>
       <c r="D8" t="n">
-        <v>31.04286240828414</v>
+        <v>31.79389940203295</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>29.84218496599028</v>
+        <v>30.50780990946962</v>
       </c>
       <c r="D9" t="n">
-        <v>30.84062238120929</v>
+        <v>31.8390597964283</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.9964739198105126</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>24.76949457814703</v>
+        <v>25.76596849795754</v>
       </c>
       <c r="D10" t="n">
-        <v>23.06125357275758</v>
+        <v>23.63066724122073</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>18.8358114536793</v>
+        <v>20.43507846389736</v>
       </c>
       <c r="D11" t="n">
-        <v>22.38973814305275</v>
+        <v>23.10052348092744</v>
       </c>
     </row>
     <row r="12">
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>14.31977201414398</v>
+        <v>15.62156946997525</v>
       </c>
       <c r="D12" t="n">
         <v>21.26269177857742</v>
@@ -2803,7 +2803,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>12.74799393964483</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
         <v>15.86995163914969</v>
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.90605532002857</v>
+        <v>13.21334235145782</v>
       </c>
       <c r="D14" t="n">
-        <v>13.82791641431633</v>
+        <v>14.74977750860408</v>
       </c>
     </row>
     <row r="15">
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>11.46681318560274</v>
+        <v>12.541826921753</v>
       </c>
       <c r="D15" t="n">
         <v>12.18348900970292</v>
@@ -2848,7 +2848,7 @@
         <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
-        <v>8.679631453246051</v>
+        <v>9.092947236733956</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.27768003604838</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>28.35778243716912</v>
+        <v>29.42788743479814</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>3.21031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.582397372796611</v>
+        <v>2.055779692692821</v>
       </c>
       <c r="C2" t="n">
-        <v>5.901285450227578</v>
+        <v>9.749736450875075</v>
       </c>
       <c r="D2" t="n">
-        <v>20.34672117051515</v>
+        <v>16.29995713360979</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.95754816900591</v>
+        <v>10.26908098642164</v>
       </c>
       <c r="C3" t="n">
-        <v>20.03256190515617</v>
+        <v>19.10481032464293</v>
       </c>
       <c r="D3" t="n">
-        <v>100.8009455335413</v>
+        <v>80.85183218324607</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>46.40525048433824</v>
+        <v>30.9495963763807</v>
       </c>
       <c r="C4" t="n">
-        <v>83.44266437475339</v>
+        <v>89.33904108645974</v>
       </c>
       <c r="D4" t="n">
-        <v>213.3799182749315</v>
+        <v>155.2329652478014</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>56.59775514982863</v>
+        <v>42.58330667170541</v>
       </c>
       <c r="C5" t="n">
-        <v>198.3866673356742</v>
+        <v>215.1745530782947</v>
       </c>
       <c r="D5" t="n">
-        <v>188.0537727484765</v>
+        <v>132.4623089955009</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>46.12839763174064</v>
+        <v>36.06548366321083</v>
       </c>
       <c r="C6" t="n">
-        <v>257.9728624972302</v>
+        <v>290.657207067015</v>
       </c>
       <c r="D6" t="n">
-        <v>87.02407999984578</v>
+        <v>69.23284810348508</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.16371518689774</v>
+        <v>15.21119892960008</v>
       </c>
       <c r="C7" t="n">
-        <v>210.3816607861617</v>
+        <v>247.0921526910627</v>
       </c>
       <c r="D7" t="n">
-        <v>42.87881273068369</v>
+        <v>40.36357511240336</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.674501730546564</v>
+        <v>5.090361846519712</v>
       </c>
       <c r="C8" t="n">
-        <v>129.0949143699343</v>
+        <v>143.5315143608837</v>
       </c>
       <c r="D8" t="n">
-        <v>32.54493639578176</v>
+        <v>33.54631905411351</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.218749811597791</v>
+        <v>2.107812321017901</v>
       </c>
       <c r="C9" t="n">
-        <v>54.47030787472577</v>
+        <v>58.13124506386212</v>
       </c>
       <c r="D9" t="n">
-        <v>31.94999728700819</v>
+        <v>32.72655972106742</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.9964739198105126</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>29.04009709162065</v>
+        <v>30.03657101143117</v>
       </c>
       <c r="D10" t="n">
-        <v>23.91537407545231</v>
+        <v>24.91184799526281</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>22.0343454741154</v>
+        <v>23.81130881880213</v>
       </c>
       <c r="D11" t="n">
-        <v>23.27821981539612</v>
+        <v>23.81130881880213</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.27246819789088</v>
+        <v>18.00819813899924</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>21.47965802121596</v>
       </c>
     </row>
     <row r="13">
@@ -3114,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.56913593102267</v>
+        <v>15.34962535589888</v>
       </c>
       <c r="D13" t="n">
         <v>15.86995163914969</v>
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>13.82791641431633</v>
       </c>
       <c r="D14" t="n">
-        <v>13.82791641431633</v>
+        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.90016483380309</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="D15" t="n">
         <v>11.46681318560274</v>
@@ -3156,10 +3156,10 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>23.97231544229862</v>
       </c>
       <c r="D16" t="n">
-        <v>7.852999886270235</v>
+        <v>8.266315669758143</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>33.99988649347554</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.55156228333746</v>
+        <v>1.557051858935441</v>
       </c>
       <c r="C2" t="n">
-        <v>3.965278977452867</v>
+        <v>4.988260085278044</v>
       </c>
       <c r="D2" t="n">
-        <v>15.06491852166731</v>
+        <v>12.63705644906494</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.35591675275186</v>
+        <v>9.007535186464485</v>
       </c>
       <c r="C3" t="n">
-        <v>21.45118733779281</v>
+        <v>27.9798095710341</v>
       </c>
       <c r="D3" t="n">
-        <v>95.58295648546947</v>
+        <v>77.30281423239386</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.38048580755381</v>
+        <v>27.15906849028376</v>
       </c>
       <c r="C4" t="n">
-        <v>72.05831799630738</v>
+        <v>73.57708169477721</v>
       </c>
       <c r="D4" t="n">
-        <v>215.0135464547982</v>
+        <v>158.8575777718806</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>61.72738690451821</v>
+        <v>45.77398671050754</v>
       </c>
       <c r="C5" t="n">
-        <v>187.2192871998668</v>
+        <v>203.54084278297</v>
       </c>
       <c r="D5" t="n">
-        <v>209.4067853158447</v>
+        <v>147.2376119444154</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>53.21268906558563</v>
+        <v>41.90197376495812</v>
       </c>
       <c r="C6" t="n">
-        <v>288.3628626821902</v>
+        <v>321.4899754665903</v>
       </c>
       <c r="D6" t="n">
-        <v>104.6945569285841</v>
+        <v>83.20017269180445</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.94791061841269</v>
+        <v>13.65414707066464</v>
       </c>
       <c r="C7" t="n">
-        <v>263.8005168696392</v>
+        <v>307.5177421397496</v>
       </c>
       <c r="D7" t="n">
-        <v>48.62792728675301</v>
+        <v>44.91495746929157</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.589670517353839</v>
+        <v>4.172427743048944</v>
       </c>
       <c r="C8" t="n">
-        <v>165.7288299539041</v>
+        <v>187.7592484372025</v>
       </c>
       <c r="D8" t="n">
-        <v>33.79666471869644</v>
+        <v>34.79804737702819</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.553124868118454</v>
+        <v>1.664062358698343</v>
       </c>
       <c r="C9" t="n">
-        <v>59.90624491314035</v>
+        <v>66.78436932909349</v>
       </c>
       <c r="D9" t="n">
-        <v>31.61718481526852</v>
+        <v>32.28280975874785</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.2847068342315751</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>29.46715734296802</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D10" t="n">
-        <v>24.34243432679967</v>
+        <v>25.33890824661018</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>21.32356013624072</v>
+        <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
-        <v>23.63361248433346</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.83853571261379</v>
+        <v>16.92336692580652</v>
       </c>
       <c r="D12" t="n">
-        <v>19.7439280801076</v>
+        <v>19.96089432274615</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.18701508989241</v>
+        <v>11.44717823151781</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>10.75504610002381</v>
+        <v>11.36962016288231</v>
       </c>
       <c r="D14" t="n">
         <v>10.75504610002381</v>
@@ -3453,10 +3453,10 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>20.0669230748048</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>6.808420328951629</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>27.69215749368978</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.987859174650544</v>
+        <v>1.956623174563893</v>
       </c>
       <c r="C2" t="n">
-        <v>10.88660029239288</v>
+        <v>7.508406442079605</v>
       </c>
       <c r="D2" t="n">
-        <v>21.06437874231957</v>
+        <v>14.87053247622644</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.76762889372977</v>
+        <v>7.225663103256524</v>
       </c>
       <c r="C3" t="n">
-        <v>18.60411899547706</v>
+        <v>24.08717992369549</v>
       </c>
       <c r="D3" t="n">
-        <v>87.34609324683872</v>
+        <v>70.66129101316419</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.44582093538184</v>
+        <v>22.47515019332223</v>
       </c>
       <c r="C4" t="n">
-        <v>63.99227885821559</v>
+        <v>71.70096183196155</v>
       </c>
       <c r="D4" t="n">
-        <v>212.9715112299648</v>
+        <v>160.0827989067807</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>63.2245521534946</v>
+        <v>44.27682146153116</v>
       </c>
       <c r="C5" t="n">
-        <v>164.6390900021901</v>
+        <v>174.8738098189631</v>
       </c>
       <c r="D5" t="n">
-        <v>226.4891953697392</v>
+        <v>164.0254976870359</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>63.47686131348603</v>
+        <v>49.06676851055134</v>
       </c>
       <c r="C6" t="n">
-        <v>292.8307964842174</v>
+        <v>323.4623066044222</v>
       </c>
       <c r="D6" t="n">
-        <v>133.1122259757123</v>
+        <v>101.8769410173958</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>31.02126395879071</v>
+        <v>25.09248957284423</v>
       </c>
       <c r="C7" t="n">
-        <v>321.950415139882</v>
+        <v>369.3207236174948</v>
       </c>
       <c r="D7" t="n">
-        <v>60.7250224984822</v>
+        <v>53.71828913327272</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.344855486097888</v>
+        <v>7.260024272905162</v>
       </c>
       <c r="C8" t="n">
-        <v>234.4904391593507</v>
+        <v>272.0422888467912</v>
       </c>
       <c r="D8" t="n">
-        <v>37.05115835827462</v>
+        <v>37.38495257771854</v>
       </c>
     </row>
     <row r="9">
@@ -3680,10 +3680,10 @@
         <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>109.1624907306113</v>
+        <v>124.0281144683165</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>33.28124717396686</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
-        <v>42.70602513473626</v>
+        <v>47.68839473378882</v>
       </c>
       <c r="D10" t="n">
-        <v>25.62361508084176</v>
+        <v>26.47773558353648</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>25.23287949455151</v>
+        <v>27.54293184264426</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>24.52209415667683</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.22516438163779</v>
+        <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>20.39482680802324</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>12.74799393964483</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>16.65044106402591</v>
       </c>
     </row>
     <row r="14">
@@ -3750,7 +3750,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>11.98419422574081</v>
       </c>
       <c r="D14" t="n">
         <v>10.75504610002381</v>
@@ -3764,10 +3764,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>6.091744504851459</v>
+        <v>6.450082416901544</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>26.03889435973815</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.083710596768237</v>
+        <v>4.111559385385641</v>
       </c>
       <c r="C2" t="n">
-        <v>8.486227155509429</v>
+        <v>5.002986300841745</v>
       </c>
       <c r="D2" t="n">
-        <v>19.9451863594782</v>
+        <v>9.191122007158638</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.915790681613027</v>
+        <v>1.413716694115407</v>
       </c>
       <c r="C2" t="n">
-        <v>6.444191930676063</v>
+        <v>4.384485247166255</v>
       </c>
       <c r="D2" t="n">
-        <v>15.67163860289183</v>
+        <v>11.06331487915731</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.0971362694582</v>
+        <v>9.807659565425636</v>
       </c>
       <c r="C3" t="n">
-        <v>27.98471830955533</v>
+        <v>29.1480893390878</v>
       </c>
       <c r="D3" t="n">
-        <v>96.03946916794422</v>
+        <v>76.13453446434015</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>49.53211692236432</v>
+        <v>32.51941095547134</v>
       </c>
       <c r="C4" t="n">
-        <v>93.29548433457438</v>
+        <v>103.9140675037079</v>
       </c>
       <c r="D4" t="n">
-        <v>216.3536320710951</v>
+        <v>163.3883434269797</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.32466505713199</v>
+        <v>28.44613973055134</v>
       </c>
       <c r="C5" t="n">
-        <v>246.1977805324939</v>
+        <v>267.3544435590127</v>
       </c>
       <c r="D5" t="n">
-        <v>203.6144738607885</v>
+        <v>149.1274762750905</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>19.24029150782899</v>
+        <v>15.57739082328414</v>
       </c>
       <c r="C6" t="n">
-        <v>263.6885976313551</v>
+        <v>303.4572336349849</v>
       </c>
       <c r="D6" t="n">
-        <v>99.09957676208155</v>
+        <v>79.69827863075608</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.509568116233099</v>
+        <v>4.790928796724434</v>
       </c>
       <c r="C7" t="n">
-        <v>164.8678372172796</v>
+        <v>191.277832209223</v>
       </c>
       <c r="D7" t="n">
-        <v>33.17718191731671</v>
+        <v>33.11729530735765</v>
       </c>
     </row>
     <row r="8">
@@ -4288,10 +4288,10 @@
         <v>1.585522542358599</v>
       </c>
       <c r="C8" t="n">
-        <v>80.44440688598364</v>
+        <v>91.37616757277186</v>
       </c>
       <c r="D8" t="n">
-        <v>23.94973524510094</v>
+        <v>24.53387512912779</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.2218749811597791</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>32.61562223048752</v>
+        <v>36.38749691020377</v>
       </c>
       <c r="D9" t="n">
-        <v>19.52499834206056</v>
+        <v>20.1906232855399</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>19.78712497909446</v>
+        <v>21.49536598448391</v>
       </c>
       <c r="D10" t="n">
-        <v>18.64829764216817</v>
+        <v>19.21771131063132</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>14.57109942643116</v>
+        <v>15.81497376771187</v>
       </c>
       <c r="D11" t="n">
-        <v>16.17036643664921</v>
+        <v>16.34806277111788</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.41437964665016</v>
+        <v>10.63134588928871</v>
       </c>
       <c r="D12" t="n">
-        <v>13.0179745583127</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -4358,7 +4358,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.365873098514571</v>
+        <v>9.886199381765381</v>
       </c>
       <c r="D13" t="n">
         <v>8.845546815263763</v>
@@ -4372,10 +4372,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>4.916592502868027</v>
+        <v>5.223879534297279</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>21.85861263505523</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.440665850486575</v>
+        <v>5.482079180514189</v>
       </c>
       <c r="C2" t="n">
-        <v>5.213080309550564</v>
+        <v>6.172247816599698</v>
       </c>
       <c r="D2" t="n">
-        <v>32.76975662005428</v>
+        <v>22.35635872110836</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.16094987023424</v>
+        <v>8.742463306317847</v>
       </c>
       <c r="C3" t="n">
-        <v>21.38246499849553</v>
+        <v>12.80689880189964</v>
       </c>
       <c r="D3" t="n">
-        <v>19.89020848804038</v>
+        <v>10.85812960896972</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.454950097693773</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>4.68784528777852</v>
       </c>
       <c r="C5" t="n">
-        <v>9.449321653375552</v>
+        <v>9.424777960769381</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>8.130834486572086</v>
       </c>
       <c r="C6" t="n">
-        <v>18.43525839034661</v>
+        <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>32.52333794628834</v>
       </c>
     </row>
     <row r="7">
@@ -4585,10 +4585,10 @@
         <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>20.72076704583318</v>
+        <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>32.69808903764427</v>
       </c>
     </row>
     <row r="8">
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.845546815263761</v>
+        <v>8.762098260402782</v>
       </c>
       <c r="C8" t="n">
         <v>21.69662426385451</v>
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.764061755811273</v>
+        <v>8.874999246391162</v>
       </c>
       <c r="C9" t="n">
         <v>22.74218556887735</v>
       </c>
       <c r="D9" t="n">
-        <v>39.60468413702056</v>
+        <v>39.2718716652809</v>
       </c>
     </row>
     <row r="10">
@@ -4630,7 +4630,7 @@
         <v>25.62361508084176</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>50.67781649322036</v>
       </c>
     </row>
     <row r="11">
@@ -4638,7 +4638,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.930157044278233</v>
+        <v>6.75246070980956</v>
       </c>
       <c r="C11" t="n">
         <v>27.36523550817559</v>
@@ -4697,7 +4697,7 @@
         <v>5.375068680751286</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>26.15866757965626</v>
       </c>
       <c r="D15" t="n">
         <v>42.28387362191012</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39573983238621</v>
+        <v>13.39886016340244</v>
       </c>
       <c r="C21" t="n">
-        <v>70.13063794602191</v>
+        <v>70.14697379663629</v>
       </c>
       <c r="D21" t="n">
-        <v>1.575969392045436</v>
+        <v>1.576336489812051</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.42652047199962</v>
+        <v>4.070325981807276</v>
       </c>
       <c r="C2" t="n">
-        <v>5.124723016168351</v>
+        <v>4.630903920932204</v>
       </c>
       <c r="D2" t="n">
-        <v>41.68304402691108</v>
+        <v>21.98427634119883</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.48693116577319</v>
+        <v>14.82929907264807</v>
       </c>
       <c r="C3" t="n">
-        <v>20.72469403665017</v>
+        <v>19.8509385798705</v>
       </c>
       <c r="D3" t="n">
-        <v>42.7992911666397</v>
+        <v>27.01278808235099</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>19.4376227963826</v>
+        <v>10.29951516525329</v>
       </c>
       <c r="C4" t="n">
-        <v>33.13202152292136</v>
+        <v>20.05023336383261</v>
       </c>
       <c r="D4" t="n">
-        <v>25.00216878405352</v>
+        <v>20.76494569252429</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.117048960983624</v>
+        <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.522330836388309</v>
+        <v>5.399612373357458</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>29.10881943091793</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.366053024963819</v>
+        <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.58368222013712</v>
+        <v>16.54343056426301</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>34.77743067523902</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>9.521970983489814</v>
       </c>
       <c r="C7" t="n">
-        <v>24.3139636433765</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>35.27321326588365</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.513135254151592</v>
+        <v>9.596583809012571</v>
       </c>
       <c r="C8" t="n">
-        <v>25.20146356801562</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.96770980341364</v>
+        <v>36.80081269369168</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>9.318749208710722</v>
       </c>
       <c r="C9" t="n">
         <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
-        <v>40.04843409934012</v>
+        <v>40.27030908049991</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
-        <v>49.68134257340984</v>
+        <v>50.1084028247572</v>
       </c>
     </row>
     <row r="11">
@@ -4963,10 +4963,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.292021036517808</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>29.07347651356504</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -4980,7 +4980,7 @@
         <v>5.203262832508096</v>
       </c>
       <c r="C13" t="n">
-        <v>26.53664044579129</v>
+        <v>26.79680358741669</v>
       </c>
       <c r="D13" t="n">
         <v>44.74806035956962</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>5.0167307687012</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5025,7 +5025,7 @@
         <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>40.5049467818149</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43205587665261</v>
+        <v>15.44254932285268</v>
       </c>
       <c r="C21" t="n">
-        <v>86.09462752237772</v>
+        <v>86.15316990644126</v>
       </c>
       <c r="D21" t="n">
-        <v>3.248853868768971</v>
+        <v>3.251063015337406</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.625414345334224</v>
+        <v>3.853359739168731</v>
       </c>
       <c r="C2" t="n">
-        <v>6.828055283036567</v>
+        <v>11.08589507635498</v>
       </c>
       <c r="D2" t="n">
-        <v>41.37772049089032</v>
+        <v>22.54681777573225</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.3003991019663</v>
+        <v>14.41696503686441</v>
       </c>
       <c r="C3" t="n">
-        <v>20.24363766156923</v>
+        <v>18.74156367407161</v>
       </c>
       <c r="D3" t="n">
-        <v>66.62630794870978</v>
+        <v>38.33233911231671</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.85124167950677</v>
+        <v>20.65008121112741</v>
       </c>
       <c r="C4" t="n">
-        <v>43.99309637500382</v>
+        <v>37.50963453615788</v>
       </c>
       <c r="D4" t="n">
-        <v>39.73034784316418</v>
+        <v>29.62227348023901</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>16.22338081267855</v>
+        <v>9.621127501618743</v>
       </c>
       <c r="C5" t="n">
-        <v>36.66827675361837</v>
+        <v>23.36559536107409</v>
       </c>
       <c r="D5" t="n">
-        <v>31.90680038802134</v>
+        <v>29.89421759431538</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.997496725243765</v>
+        <v>5.916993413495527</v>
       </c>
       <c r="C6" t="n">
-        <v>12.47801332097696</v>
+        <v>12.19625172985813</v>
       </c>
       <c r="D6" t="n">
-        <v>36.10573531908495</v>
+        <v>36.6290068454485</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.19419042345839</v>
+        <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>37.42913122440964</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>10.34762080276138</v>
       </c>
       <c r="C8" t="n">
-        <v>29.45733986592554</v>
+        <v>29.87458264023044</v>
       </c>
       <c r="D8" t="n">
-        <v>38.13598957146735</v>
+        <v>38.55323234577224</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
-        <v>29.39843500367073</v>
+        <v>29.50937249425062</v>
       </c>
       <c r="D9" t="n">
-        <v>41.04687151455913</v>
+        <v>41.26874649571891</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>9.537678946757763</v>
       </c>
       <c r="C10" t="n">
-        <v>29.60951076008381</v>
+        <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
-        <v>49.39663573917827</v>
+        <v>49.25428232206248</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.174031385558941</v>
+        <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>31.27455486648638</v>
       </c>
       <c r="D11" t="n">
-        <v>49.04418831335365</v>
+        <v>49.75497365122833</v>
       </c>
     </row>
     <row r="12">
@@ -5277,10 +5277,10 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>31.89403766786613</v>
+        <v>32.11100391050467</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>45.77987719673301</v>
       </c>
     </row>
     <row r="13">
@@ -5291,10 +5291,10 @@
         <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>45.52854978444583</v>
       </c>
     </row>
     <row r="14">
@@ -5305,7 +5305,7 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>27.3485457972034</v>
+        <v>27.65583282863265</v>
       </c>
       <c r="D14" t="n">
         <v>45.47848065152925</v>
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
         <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>43.00054944601029</v>
       </c>
     </row>
     <row r="16">
@@ -5350,7 +5350,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.71314854493277</v>
+        <v>16.73844290794894</v>
       </c>
       <c r="C21" t="n">
-        <v>101.1145486968432</v>
+        <v>102.1045017384885</v>
       </c>
       <c r="D21" t="n">
-        <v>4.178287136233192</v>
+        <v>5.021532872384681</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.085273181549231</v>
+        <v>4.997095814616265</v>
       </c>
       <c r="C2" t="n">
-        <v>12.10593094106742</v>
+        <v>10.29067943591507</v>
       </c>
       <c r="D2" t="n">
-        <v>42.91906438655781</v>
+        <v>18.41856867937441</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.57252314249191</v>
+        <v>13.75428533649781</v>
       </c>
       <c r="C3" t="n">
-        <v>23.6846633649543</v>
+        <v>32.74619467515236</v>
       </c>
       <c r="D3" t="n">
-        <v>82.23609644623407</v>
+        <v>46.94226647856124</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.89251614081414</v>
+        <v>24.68310078017331</v>
       </c>
       <c r="C4" t="n">
-        <v>47.13272553318512</v>
+        <v>42.39775635560276</v>
       </c>
       <c r="D4" t="n">
-        <v>61.19724314422493</v>
+        <v>41.21082338116835</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.37313054753858</v>
+        <v>20.19945901487813</v>
       </c>
       <c r="C5" t="n">
-        <v>60.27930904075417</v>
+        <v>48.62105505282329</v>
       </c>
       <c r="D5" t="n">
-        <v>38.60722846950583</v>
+        <v>33.91938318172731</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>13.56480802957818</v>
+        <v>9.499390786292139</v>
       </c>
       <c r="C6" t="n">
-        <v>35.66296710446964</v>
+        <v>25.318291544821</v>
       </c>
       <c r="D6" t="n">
-        <v>37.8768081775462</v>
+        <v>38.23907308041327</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.623671834103982</v>
+        <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>21.02020009562846</v>
       </c>
       <c r="D7" t="n">
-        <v>39.76470901281281</v>
+        <v>39.46527596301753</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>10.76486357706628</v>
       </c>
       <c r="C8" t="n">
-        <v>31.37665662772806</v>
+        <v>31.87734795689393</v>
       </c>
       <c r="D8" t="n">
-        <v>39.55461500410399</v>
+        <v>40.38910055271378</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>33.39218466454675</v>
+        <v>34.27968458918587</v>
       </c>
       <c r="D9" t="n">
-        <v>42.04530892977813</v>
+        <v>41.93437143919824</v>
       </c>
     </row>
     <row r="10">
@@ -5563,7 +5563,7 @@
         <v>33.16834618797849</v>
       </c>
       <c r="D10" t="n">
-        <v>48.82722207071512</v>
+        <v>49.25428232206248</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.707120388964958</v>
+        <v>9.062513057902304</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>33.7623035490478</v>
       </c>
       <c r="D11" t="n">
-        <v>50.28806265463436</v>
+        <v>50.82115165804038</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.159886007071988</v>
+        <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
-        <v>34.06370009425158</v>
+        <v>34.49763257952867</v>
       </c>
       <c r="D12" t="n">
-        <v>47.51560713784138</v>
+        <v>46.86470840992573</v>
       </c>
     </row>
     <row r="13">
@@ -5605,7 +5605,7 @@
         <v>33.04071898642641</v>
       </c>
       <c r="D13" t="n">
-        <v>45.26838664282043</v>
+        <v>46.30903920932205</v>
       </c>
     </row>
     <row r="14">
@@ -5616,10 +5616,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>30.11412908006666</v>
+        <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5630,7 +5630,7 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
         <v>43.71722527011046</v>
@@ -5647,7 +5647,7 @@
         <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5661,7 +5661,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.77765165941727</v>
       </c>
     </row>
     <row r="18">
@@ -5689,7 +5689,7 @@
         <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
-        <v>25.27607639353838</v>
+        <v>24.67426505083508</v>
       </c>
     </row>
     <row r="20">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.02076458118837</v>
+        <v>18.06773558664349</v>
       </c>
       <c r="C21" t="n">
-        <v>116.7059039543628</v>
+        <v>117.870465493817</v>
       </c>
       <c r="D21" t="n">
-        <v>6.006921527062791</v>
+        <v>6.882946890149898</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.816274310585604</v>
+        <v>5.866924280578939</v>
       </c>
       <c r="C2" t="n">
-        <v>6.773077411598745</v>
+        <v>9.450303401079797</v>
       </c>
       <c r="D2" t="n">
-        <v>37.15816885803753</v>
+        <v>25.25644143945344</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.89511722656161</v>
+        <v>14.1273494641116</v>
       </c>
       <c r="C3" t="n">
-        <v>34.27281235525615</v>
+        <v>34.6556939599124</v>
       </c>
       <c r="D3" t="n">
-        <v>89.87900232379549</v>
+        <v>47.51168014702439</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.86101809882023</v>
+        <v>18.63357142660446</v>
       </c>
       <c r="C4" t="n">
-        <v>44.78438502462675</v>
+        <v>53.71828913327272</v>
       </c>
       <c r="D4" t="n">
-        <v>74.20245498238242</v>
+        <v>47.38797993628929</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26.94897448157495</v>
+        <v>17.57328390601791</v>
       </c>
       <c r="C5" t="n">
-        <v>54.51154127830416</v>
+        <v>48.22835597112457</v>
       </c>
       <c r="D5" t="n">
-        <v>41.35612204139689</v>
+        <v>33.35487825178539</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>15.41638419978766</v>
+        <v>10.18366893615217</v>
       </c>
       <c r="C6" t="n">
-        <v>44.59883470852411</v>
+        <v>35.34095385747668</v>
       </c>
       <c r="D6" t="n">
-        <v>31.63780151705772</v>
+        <v>31.35603992593888</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.048547605864599</v>
+        <v>5.030475236560656</v>
       </c>
       <c r="C7" t="n">
-        <v>22.93657161431823</v>
+        <v>18.74450891718435</v>
       </c>
       <c r="D7" t="n">
-        <v>31.14103717870882</v>
+        <v>30.72183090899544</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.60902773399829</v>
+        <v>18.69247628885927</v>
       </c>
       <c r="D8" t="n">
-        <v>29.45733986592554</v>
+        <v>30.37527396939631</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>21.41093568191868</v>
+        <v>21.96562313481813</v>
       </c>
       <c r="D9" t="n">
-        <v>30.17499743772996</v>
+        <v>29.95312245657017</v>
       </c>
     </row>
     <row r="10">
@@ -5871,10 +5871,10 @@
         <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.06830573313655</v>
+        <v>21.49536598448391</v>
       </c>
       <c r="D10" t="n">
-        <v>33.16834618797849</v>
+        <v>33.73775985644164</v>
       </c>
     </row>
     <row r="11">
@@ -5882,10 +5882,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.553926689373453</v>
+        <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.07968579496001</v>
+        <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
         <v>34.47308888692249</v>
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.820561154301086</v>
+        <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>20.17786056538469</v>
       </c>
       <c r="D12" t="n">
-        <v>31.89403766786613</v>
+        <v>32.11100391050467</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.081305133003238</v>
+        <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>18.73174619702914</v>
+        <v>19.25207248027995</v>
       </c>
       <c r="D13" t="n">
-        <v>30.17892442854696</v>
+        <v>30.43908757017236</v>
       </c>
     </row>
     <row r="14">
@@ -5927,7 +5927,7 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
         <v>29.80684204863741</v>
@@ -5941,10 +5941,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
-        <v>27.95035713990669</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -5958,7 +5958,7 @@
         <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -5972,7 +5972,7 @@
         <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>23.13881164139307</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -5983,7 +5983,7 @@
         <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -6011,7 +6011,7 @@
         <v>1.34499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.08745766113597</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.035035002040011</v>
+        <v>7.063278376576924</v>
       </c>
       <c r="C21" t="n">
-        <v>65.95345314412511</v>
+        <v>66.21823478040865</v>
       </c>
       <c r="D21" t="n">
-        <v>4.396896876275007</v>
+        <v>5.297458782432693</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.913066422678538</v>
+        <v>5.138467484027806</v>
       </c>
       <c r="C2" t="n">
-        <v>7.200137662946108</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="D2" t="n">
-        <v>35.5196319396496</v>
+        <v>30.63740060643021</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.20713307006285</v>
+        <v>18.09361018926871</v>
       </c>
       <c r="C3" t="n">
-        <v>29.35425635697963</v>
+        <v>36.1675854244525</v>
       </c>
       <c r="D3" t="n">
-        <v>99.37250262386215</v>
+        <v>57.80039608753097</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.57420890045992</v>
+        <v>24.36403277629309</v>
       </c>
       <c r="C4" t="n">
-        <v>69.79931652883548</v>
+        <v>74.95545547153972</v>
       </c>
       <c r="D4" t="n">
-        <v>104.0927455858808</v>
+        <v>62.02681995431348</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.29382996767284</v>
+        <v>23.6846633649543</v>
       </c>
       <c r="C5" t="n">
-        <v>71.27488332831845</v>
+        <v>79.98789420350889</v>
       </c>
       <c r="D5" t="n">
-        <v>59.54299826256906</v>
+        <v>43.98229715025711</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>27.29062268265284</v>
+        <v>18.19374845510189</v>
       </c>
       <c r="C6" t="n">
-        <v>68.54856995362505</v>
+        <v>60.09572222006002</v>
       </c>
       <c r="D6" t="n">
-        <v>37.47429161880501</v>
+        <v>35.05919226635785</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>12.87562114119692</v>
+        <v>9.222537933694536</v>
       </c>
       <c r="C7" t="n">
-        <v>46.05280305851362</v>
+        <v>37.96811071404115</v>
       </c>
       <c r="D7" t="n">
-        <v>33.77604801690726</v>
+        <v>33.47661496711198</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.9248473951295</v>
+        <v>5.424156065963627</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>22.69800692218626</v>
       </c>
       <c r="D8" t="n">
-        <v>31.54355373745002</v>
+        <v>32.3780392860598</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>23.07499804061703</v>
+        <v>23.40781051235669</v>
       </c>
       <c r="D9" t="n">
-        <v>31.06249736236907</v>
+        <v>31.17343485294896</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.05772749256809</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>34.16482010778901</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.909319358310797</v>
+        <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>22.92282714645877</v>
+        <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
-        <v>34.82848155585983</v>
+        <v>35.36157055926586</v>
       </c>
     </row>
     <row r="12">
@@ -6207,10 +6207,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>21.47965802121596</v>
+        <v>21.91359050649305</v>
       </c>
       <c r="D12" t="n">
         <v>32.97886888105885</v>
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>20.81305133003238</v>
+        <v>21.33337761328319</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>31.21957699504857</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>19.0517959486136</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -6252,7 +6252,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -6283,7 +6283,7 @@
         <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>23.13881164139307</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -6294,7 +6294,7 @@
         <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -6311,7 +6311,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6322,7 +6322,7 @@
         <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.247113586363468</v>
+        <v>7.286792272936624</v>
       </c>
       <c r="C21" t="n">
-        <v>75.18880345852098</v>
+        <v>75.60046983171748</v>
       </c>
       <c r="D21" t="n">
-        <v>5.435335189772601</v>
+        <v>6.375943238819546</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.851797154387737</v>
+        <v>3.632466505713198</v>
       </c>
       <c r="C2" t="n">
-        <v>6.989061906533043</v>
+        <v>7.152032025438014</v>
       </c>
       <c r="D2" t="n">
-        <v>33.63565809519997</v>
+        <v>21.80854350213865</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.14193681095506</v>
+        <v>17.93162181806799</v>
       </c>
       <c r="C3" t="n">
-        <v>28.52467954689108</v>
+        <v>29.5947845445201</v>
       </c>
       <c r="D3" t="n">
-        <v>104.2665149295325</v>
+        <v>68.89905388404115</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.3219407981975</v>
+        <v>30.63052837250048</v>
       </c>
       <c r="C4" t="n">
-        <v>71.84135175366885</v>
+        <v>84.19566486391069</v>
       </c>
       <c r="D4" t="n">
-        <v>129.0566262094687</v>
+        <v>77.07406701730434</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.73686022419541</v>
+        <v>30.55689729468198</v>
       </c>
       <c r="C5" t="n">
-        <v>101.7336058525757</v>
+        <v>113.4164035331128</v>
       </c>
       <c r="D5" t="n">
-        <v>81.4605157598791</v>
+        <v>55.93507544946203</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.11831811279092</v>
+        <v>25.92206638293279</v>
       </c>
       <c r="C6" t="n">
-        <v>92.37755023110364</v>
+        <v>96.32221250676733</v>
       </c>
       <c r="D6" t="n">
-        <v>47.33594730796422</v>
+        <v>41.29819892684633</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.75691178444107</v>
+        <v>15.81006502919063</v>
       </c>
       <c r="C7" t="n">
-        <v>73.95996329943345</v>
+        <v>65.15663163545231</v>
       </c>
       <c r="D7" t="n">
-        <v>36.71049190490098</v>
+        <v>36.05173919535137</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.09727513817844</v>
+        <v>8.011061266653972</v>
       </c>
       <c r="C8" t="n">
-        <v>43.81049130201391</v>
+        <v>38.05254101660637</v>
       </c>
       <c r="D8" t="n">
-        <v>33.79666471869644</v>
+        <v>34.54770171244525</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>5.546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>28.17812260729194</v>
+        <v>26.62499773917349</v>
       </c>
       <c r="D9" t="n">
-        <v>32.06093477758807</v>
+        <v>32.72655972106742</v>
       </c>
     </row>
     <row r="10">
@@ -6493,7 +6493,7 @@
         <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>26.47773558353648</v>
+        <v>26.90479583488384</v>
       </c>
       <c r="D10" t="n">
         <v>34.30717352490479</v>
@@ -6507,10 +6507,10 @@
         <v>4.264712027248144</v>
       </c>
       <c r="C11" t="n">
-        <v>25.58827216348886</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>35.53926689373453</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.0832529328785</v>
+        <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
-        <v>33.41280136633594</v>
+        <v>34.06370009425158</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>22.63419332141022</v>
+        <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>31.47974013667398</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>20.89551813718911</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>18.99190933865455</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -6577,7 +6577,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -6591,10 +6591,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>23.13881164139307</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -6622,7 +6622,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6633,7 +6633,7 @@
         <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.444550373376908</v>
+        <v>7.496401793533127</v>
       </c>
       <c r="C21" t="n">
-        <v>83.75119170049021</v>
+        <v>85.27157040143932</v>
       </c>
       <c r="D21" t="n">
-        <v>6.513981576704794</v>
+        <v>7.496401793533127</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_16_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_16_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497631846007</v>
+        <v>10.84497643479505</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907189398055</v>
+        <v>37.78907229934713</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.474405125329462</v>
+        <v>1.054397034361074</v>
       </c>
       <c r="C2" t="n">
-        <v>8.939794594871456</v>
+        <v>2.738094347144354</v>
       </c>
       <c r="D2" t="n">
-        <v>30.05915120862884</v>
+        <v>17.27974134244811</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.93729132011522</v>
+        <v>10.04327901444487</v>
       </c>
       <c r="C3" t="n">
-        <v>28.51486206984861</v>
+        <v>32.90818304635308</v>
       </c>
       <c r="D3" t="n">
-        <v>69.93479771202153</v>
+        <v>88.00877294720533</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.48112279500572</v>
+        <v>19.64182631886593</v>
       </c>
       <c r="C4" t="n">
-        <v>77.87811838708248</v>
+        <v>92.56800928572751</v>
       </c>
       <c r="D4" t="n">
-        <v>91.62356799424208</v>
+        <v>95.6948757237536</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.43542262126263</v>
+        <v>20.78850763742621</v>
       </c>
       <c r="C5" t="n">
-        <v>135.7266201121216</v>
+        <v>114.5454133929966</v>
       </c>
       <c r="D5" t="n">
-        <v>70.17041716104079</v>
+        <v>51.41903600992671</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.56988099901544</v>
+        <v>14.69185439405352</v>
       </c>
       <c r="C6" t="n">
-        <v>139.1902260127043</v>
+        <v>81.75111308033615</v>
       </c>
       <c r="D6" t="n">
-        <v>48.5434969841878</v>
+        <v>30.26924521733767</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.35577788403162</v>
+        <v>6.467753875577986</v>
       </c>
       <c r="C7" t="n">
-        <v>101.9868967602714</v>
+        <v>43.6573386601514</v>
       </c>
       <c r="D7" t="n">
-        <v>39.88448223273092</v>
+        <v>28.98511922018283</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.68418033886879</v>
+        <v>6.00829594999048</v>
       </c>
       <c r="C8" t="n">
-        <v>62.83676181031709</v>
+        <v>29.37389131106456</v>
       </c>
       <c r="D8" t="n">
-        <v>36.30012136452581</v>
+        <v>31.04286240828414</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.878124415953151</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>37.05312185368311</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>34.39062207976576</v>
+        <v>35.27812200440487</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.409429850399925</v>
+        <v>3.274128593663113</v>
       </c>
       <c r="C10" t="n">
-        <v>30.03657101143117</v>
+        <v>30.17892442854695</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>37.72365553568369</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>30.91916219754903</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>37.31623023842126</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>27.55471281509523</v>
+        <v>24.0832529328785</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>37.5351599764683</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>25.49598787928967</v>
+        <v>20.03256190515617</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>35.90251354430586</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.66110142005238</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>27.3485457972034</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>25.44199175555609</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>19.42584182393164</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
+        <v>24.55547357862122</v>
+      </c>
+      <c r="D17" t="n">
         <v>17.9443845382232</v>
-      </c>
-      <c r="D17" t="n">
-        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>26.21757244191107</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>11.23610247510475</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>10.83260416865931</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>84.25358797846125</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.691637233086565</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>94.22255610531042</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.653091887222386</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.319689898685966</v>
+        <v>1.398008730847458</v>
       </c>
       <c r="C2" t="n">
-        <v>8.084692344472483</v>
+        <v>3.951534509593412</v>
       </c>
       <c r="D2" t="n">
-        <v>33.43930855435061</v>
+        <v>18.36260906023234</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.2045066221196</v>
+        <v>6.602253311059799</v>
       </c>
       <c r="C3" t="n">
-        <v>31.56318869153495</v>
+        <v>20.14055415262332</v>
       </c>
       <c r="D3" t="n">
-        <v>76.16398689546754</v>
+        <v>81.563599268825</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.15830772675777</v>
+        <v>19.76945352041802</v>
       </c>
       <c r="C4" t="n">
-        <v>74.4577093854866</v>
+        <v>86.86307337634929</v>
       </c>
       <c r="D4" t="n">
-        <v>103.5567113393621</v>
+        <v>117.0596692635727</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.92691836819179</v>
+        <v>25.54998400302325</v>
       </c>
       <c r="C5" t="n">
-        <v>138.0582709097077</v>
+        <v>146.1576894697439</v>
       </c>
       <c r="D5" t="n">
-        <v>83.64490440182826</v>
+        <v>72.74750488468867</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.22398701195107</v>
+        <v>20.97111271041612</v>
       </c>
       <c r="C6" t="n">
-        <v>175.4167162994116</v>
+        <v>133.5952458462017</v>
       </c>
       <c r="D6" t="n">
-        <v>58.08313942635406</v>
+        <v>38.64158963915446</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>30.84160412891355</v>
+        <v>11.31856928226148</v>
       </c>
       <c r="C7" t="n">
-        <v>147.2611738893173</v>
+        <v>80.72715022480672</v>
       </c>
       <c r="D7" t="n">
-        <v>43.83699849002857</v>
+        <v>31.20092378866788</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>18.44213062427633</v>
+        <v>6.67588438887831</v>
       </c>
       <c r="C8" t="n">
-        <v>96.96722074845746</v>
+        <v>43.47669708257</v>
       </c>
       <c r="D8" t="n">
-        <v>38.7201294554942</v>
+        <v>32.3780392860598</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.540624189870499</v>
+        <v>6.212499472473814</v>
       </c>
       <c r="C9" t="n">
-        <v>55.80155776168444</v>
+        <v>34.72343455150543</v>
       </c>
       <c r="D9" t="n">
-        <v>35.49999698556465</v>
+        <v>35.61093447614454</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.121196935978863</v>
+        <v>3.98589567924205</v>
       </c>
       <c r="C10" t="n">
-        <v>37.01188845010476</v>
+        <v>34.16482010778901</v>
       </c>
       <c r="D10" t="n">
-        <v>35.87306111317846</v>
+        <v>38.57777603837842</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>32.16303653882975</v>
+        <v>33.7623035490478</v>
       </c>
       <c r="D11" t="n">
-        <v>36.42774856607789</v>
+        <v>38.20471191076462</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>30.59224021203486</v>
+        <v>28.63954402828795</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>37.96909246174538</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>27.83745615391831</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>36.68300296918207</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>25.81211064005714</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>28.88498095434966</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>25.083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.66578917439536</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>21.49242074137117</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>26.44435616159209</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>16.99994324673777</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>8.560839981032187</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>50.2949348885641</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>9.095892479846698</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>45.7376620454504</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.870803157930674</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>102.3204410530988</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9.838503947413344</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.778566987196725</v>
+        <v>0.7451465075233291</v>
       </c>
       <c r="C2" t="n">
-        <v>12.96496018228338</v>
+        <v>1.706277509980957</v>
       </c>
       <c r="D2" t="n">
-        <v>31.63092928312799</v>
+        <v>12.5123744906256</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.53830084156352</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C3" t="n">
-        <v>31.21466825652734</v>
+        <v>19.18335014098268</v>
       </c>
       <c r="D3" t="n">
-        <v>82.2115527536279</v>
+        <v>80.70457002760905</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.55471281509523</v>
+        <v>21.42860714059513</v>
       </c>
       <c r="C4" t="n">
-        <v>75.47872699790328</v>
+        <v>80.97945938479815</v>
       </c>
       <c r="D4" t="n">
-        <v>113.0138869743716</v>
+        <v>129.1459652505552</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.56505437595222</v>
+        <v>25.96722677732814</v>
       </c>
       <c r="C5" t="n">
-        <v>137.3465038241288</v>
+        <v>168.9587799008761</v>
       </c>
       <c r="D5" t="n">
-        <v>97.73298395777</v>
+        <v>82.71224408279379</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>48.50324532831367</v>
+        <v>16.30192062901829</v>
       </c>
       <c r="C6" t="n">
-        <v>192.6846766694088</v>
+        <v>169.7814844770349</v>
       </c>
       <c r="D6" t="n">
-        <v>67.3812719332756</v>
+        <v>39.16486116551801</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>38.80652325346792</v>
+        <v>4.371722527011046</v>
       </c>
       <c r="C7" t="n">
-        <v>191.3976054291412</v>
+        <v>76.83452057746811</v>
       </c>
       <c r="D7" t="n">
-        <v>49.22679338634357</v>
+        <v>33.0574086973986</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>24.61732368398877</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>139.2756380629737</v>
+        <v>40.47254910757476</v>
       </c>
       <c r="D8" t="n">
-        <v>40.72289477215769</v>
+        <v>36.46701847424777</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>13.31249886958674</v>
+        <v>2.773437264497239</v>
       </c>
       <c r="C9" t="n">
-        <v>82.42655550085793</v>
+        <v>26.07031028627404</v>
       </c>
       <c r="D9" t="n">
-        <v>36.72030938194344</v>
+        <v>40.27030908049991</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.402377690020952</v>
+        <v>1.850594422505238</v>
       </c>
       <c r="C10" t="n">
-        <v>49.11192890494669</v>
+        <v>26.47773558353648</v>
       </c>
       <c r="D10" t="n">
-        <v>36.72718161587318</v>
+        <v>29.89421759431538</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.153193699591506</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>36.96083756948391</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>30.38607319414302</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>1.301797455831271</v>
       </c>
       <c r="C12" t="n">
-        <v>32.97886888105885</v>
+        <v>18.65909686691488</v>
       </c>
       <c r="D12" t="n">
-        <v>36.23336252063703</v>
+        <v>29.94134148411922</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>17.69109363052753</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
-        <v>31.65056423721292</v>
+        <v>20.89551813718911</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>24.72531593145592</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>17.91689560250429</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.90573652485908</v>
+        <v>22.31905230834699</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>6.611089040398022</v>
       </c>
       <c r="C17" t="n">
-        <v>19.83326712119407</v>
+        <v>43.44429940832985</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>7.555530331883453</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>39.59388491227386</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.033640911805669</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>110.462562537328</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11.04625625373279</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.228788272818512</v>
+        <v>0.8256498192715676</v>
       </c>
       <c r="C2" t="n">
-        <v>8.919177893082272</v>
+        <v>5.525276079501049</v>
       </c>
       <c r="D2" t="n">
-        <v>26.09387223117598</v>
+        <v>16.58859095865835</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.56346642897544</v>
+        <v>4.501313223971626</v>
       </c>
       <c r="C3" t="n">
-        <v>49.21010367537137</v>
+        <v>12.22275891787279</v>
       </c>
       <c r="D3" t="n">
-        <v>88.32784095108553</v>
+        <v>73.03712045744146</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>20.930861054542</v>
+        <v>17.15309588860027</v>
       </c>
       <c r="C4" t="n">
-        <v>109.8614950960351</v>
+        <v>63.94122797759476</v>
       </c>
       <c r="D4" t="n">
-        <v>108.8915283642392</v>
+        <v>139.1519378522387</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.3171298706675</v>
+        <v>29.62423697564751</v>
       </c>
       <c r="C5" t="n">
-        <v>115.1344620155447</v>
+        <v>160.589380722172</v>
       </c>
       <c r="D5" t="n">
-        <v>66.51340696272142</v>
+        <v>107.2068493037517</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>24.0704902127233</v>
+        <v>24.31200014796801</v>
       </c>
       <c r="C6" t="n">
-        <v>126.0681861977414</v>
+        <v>219.1702662345792</v>
       </c>
       <c r="D6" t="n">
-        <v>32.40258297866598</v>
+        <v>53.81646390369741</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.28915790886308</v>
+        <v>9.701630813366979</v>
       </c>
       <c r="C7" t="n">
-        <v>97.91460728305563</v>
+        <v>155.7650725035032</v>
       </c>
       <c r="D7" t="n">
-        <v>28.62579956042849</v>
+        <v>36.17151241526948</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.179341034707678</v>
+        <v>4.589670517353839</v>
       </c>
       <c r="C8" t="n">
-        <v>60.75054793879262</v>
+        <v>68.34436643114171</v>
       </c>
       <c r="D8" t="n">
-        <v>27.03733177495716</v>
+        <v>37.63529824230147</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.324999547834698</v>
+        <v>3.217187226816797</v>
       </c>
       <c r="C9" t="n">
-        <v>37.49687181600267</v>
+        <v>36.60937189136354</v>
       </c>
       <c r="D9" t="n">
-        <v>27.95624762613216</v>
+        <v>41.49062147687869</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.701188845010476</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>28.89774367450487</v>
+        <v>29.60951076008381</v>
       </c>
       <c r="D10" t="n">
-        <v>28.61303684027329</v>
+        <v>31.46010518258904</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>1.421570675749381</v>
       </c>
       <c r="C11" t="n">
-        <v>26.29905750136355</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>28.96450251839364</v>
+        <v>31.45225120095506</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>21.26269177857742</v>
       </c>
       <c r="D12" t="n">
-        <v>26.68684784454105</v>
+        <v>30.8092064546734</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
+        <v>21.51009220004762</v>
+      </c>
+      <c r="D14" t="n">
         <v>20.58823110575986</v>
-      </c>
-      <c r="D14" t="n">
-        <v>23.66110142005238</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.27523351455437</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>22.57528845915541</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>37.19842051391164</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>12.39947350463721</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>46.74984392852887</v>
       </c>
       <c r="D17" t="n">
-        <v>17.47216389248049</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>73.97468951499715</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.21031499288707</v>
+        <v>0.5625414345334223</v>
       </c>
       <c r="C2" t="n">
-        <v>3.85041449605599</v>
+        <v>2.946224860444678</v>
       </c>
       <c r="D2" t="n">
-        <v>18.84170193990478</v>
+        <v>12.11280317499715</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.24087234490574</v>
+        <v>3.809181092477624</v>
       </c>
       <c r="C3" t="n">
-        <v>42.76002125846983</v>
+        <v>17.15113239319178</v>
       </c>
       <c r="D3" t="n">
-        <v>89.81518872301945</v>
+        <v>70.87727550809848</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.59750880345459</v>
+        <v>14.15385665212627</v>
       </c>
       <c r="C4" t="n">
-        <v>119.0634163279404</v>
+        <v>49.62145596345079</v>
       </c>
       <c r="D4" t="n">
-        <v>124.0153517481613</v>
+        <v>143.5550763057856</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.53235360207581</v>
+        <v>30.2869166760141</v>
       </c>
       <c r="C5" t="n">
-        <v>157.9386619207056</v>
+        <v>147.8757479521758</v>
       </c>
       <c r="D5" t="n">
-        <v>83.59581701661591</v>
+        <v>126.0073178400781</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.69943063824701</v>
+        <v>29.42396044398116</v>
       </c>
       <c r="C6" t="n">
-        <v>155.4116433299744</v>
+        <v>246.0181207026168</v>
       </c>
       <c r="D6" t="n">
-        <v>40.29190752999335</v>
+        <v>65.89196066593318</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.4507453694363</v>
+        <v>10.59992996275281</v>
       </c>
       <c r="C7" t="n">
-        <v>129.2353042916416</v>
+        <v>214.7533833131728</v>
       </c>
       <c r="D7" t="n">
-        <v>31.32069700858599</v>
+        <v>40.12402867256714</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.927612711792993</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>82.6140693123691</v>
+        <v>103.7265536921967</v>
       </c>
       <c r="D8" t="n">
-        <v>28.28906009787184</v>
+        <v>40.38910055271378</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.437499623195581</v>
+        <v>2.662499773917349</v>
       </c>
       <c r="C9" t="n">
-        <v>42.26718391093791</v>
+        <v>47.59218345877262</v>
       </c>
       <c r="D9" t="n">
-        <v>28.84374755077128</v>
+        <v>41.49062147687869</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>31.74481201682062</v>
+        <v>32.31422568528377</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>32.45657910239955</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>27.36523550817559</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>32.69612554223576</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>21.26269177857742</v>
+        <v>23.21538796232432</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>29.50740899884213</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>16.91060420565131</v>
+        <v>17.69109363052753</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>16.59349969717959</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>14.33351648200343</v>
+        <v>31.53373626040754</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>40.09163099832699</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>64.39381366925254</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.02869166760141</v>
+        <v>0.9945104244020189</v>
       </c>
       <c r="C2" t="n">
-        <v>5.85416156042373</v>
+        <v>4.317726403277472</v>
       </c>
       <c r="D2" t="n">
-        <v>23.97133369459437</v>
+        <v>15.99659709299753</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.5593184539802</v>
+        <v>2.866703296400686</v>
       </c>
       <c r="C3" t="n">
-        <v>27.96508335547039</v>
+        <v>14.12244072559037</v>
       </c>
       <c r="D3" t="n">
-        <v>84.37630644149212</v>
+        <v>64.70699118690727</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.60500293219007</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="C4" t="n">
-        <v>112.7203444108018</v>
+        <v>46.64774216728719</v>
       </c>
       <c r="D4" t="n">
-        <v>138.1053947995115</v>
+        <v>145.8268404934127</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.87658719336795</v>
+        <v>26.99806186678729</v>
       </c>
       <c r="C5" t="n">
-        <v>189.5754816900591</v>
+        <v>121.1231230114503</v>
       </c>
       <c r="D5" t="n">
-        <v>104.8261111209532</v>
+        <v>145.2250291507094</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.21390749300134</v>
+        <v>34.5359207399943</v>
       </c>
       <c r="C6" t="n">
-        <v>199.6482131356314</v>
+        <v>242.1539617387013</v>
       </c>
       <c r="D6" t="n">
-        <v>53.69570893607505</v>
+        <v>85.25300714138454</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.87668500435917</v>
+        <v>19.8823545064064</v>
       </c>
       <c r="C7" t="n">
-        <v>174.3898082007694</v>
+        <v>280.5088810482156</v>
       </c>
       <c r="D7" t="n">
-        <v>34.91389360612931</v>
+        <v>47.60985491744906</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.09865779651019</v>
+        <v>6.842781498600267</v>
       </c>
       <c r="C8" t="n">
-        <v>122.502478535917</v>
+        <v>181.3337097129071</v>
       </c>
       <c r="D8" t="n">
-        <v>29.87458264023044</v>
+        <v>41.8911745402114</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>3.217187226816797</v>
       </c>
       <c r="C9" t="n">
-        <v>67.78280674431251</v>
+        <v>80.76249314215958</v>
       </c>
       <c r="D9" t="n">
-        <v>29.84218496599028</v>
+        <v>42.48905889209769</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.562361508084175</v>
+        <v>1.565887588273662</v>
       </c>
       <c r="C10" t="n">
-        <v>40.00131020953629</v>
+        <v>42.13661146627311</v>
       </c>
       <c r="D10" t="n">
-        <v>30.32127784566274</v>
+        <v>34.59188035913637</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>32.87382187670443</v>
+        <v>31.8076438698924</v>
       </c>
       <c r="D11" t="n">
-        <v>30.20837685967435</v>
+        <v>33.22921454564179</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>25.60201663134832</v>
+        <v>26.25291535926396</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>29.72437524148068</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>20.29272504678157</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>24.71549845441346</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>20.58823110575986</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>16.90078672860884</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.5083653843506</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>32.25041208450772</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.0334615374024</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.87936820556466</v>
+        <v>40.5049467818149</v>
       </c>
       <c r="D16" t="n">
-        <v>14.46605242207675</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.3032465340878</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.812306262039612</v>
+        <v>0.667588438887831</v>
       </c>
       <c r="C2" t="n">
-        <v>2.790126975469435</v>
+        <v>2.279618169261094</v>
       </c>
       <c r="D2" t="n">
-        <v>16.7132729170977</v>
+        <v>11.51786406622358</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.18134558784518</v>
+        <v>4.250967559388689</v>
       </c>
       <c r="C3" t="n">
-        <v>27.3171298706675</v>
+        <v>17.25912464065892</v>
       </c>
       <c r="D3" t="n">
-        <v>86.17290474026379</v>
+        <v>71.20616098902116</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.78292025083699</v>
+        <v>18.25068982194821</v>
       </c>
       <c r="C4" t="n">
-        <v>109.2105963681194</v>
+        <v>66.73626369158544</v>
       </c>
       <c r="D4" t="n">
-        <v>148.0730792407294</v>
+        <v>149.6556565399753</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.42283982755667</v>
+        <v>21.18120671912494</v>
       </c>
       <c r="C5" t="n">
-        <v>223.7403017978481</v>
+        <v>193.4042977366217</v>
       </c>
       <c r="D5" t="n">
-        <v>110.7902284242526</v>
+        <v>132.2905031472577</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>27.77364255314227</v>
+        <v>12.31700669748049</v>
       </c>
       <c r="C6" t="n">
-        <v>236.7199881956952</v>
+        <v>244.086041220659</v>
       </c>
       <c r="D6" t="n">
-        <v>52.56866257159972</v>
+        <v>69.23284810348508</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.306166415004762</v>
+        <v>4.491495746929157</v>
       </c>
       <c r="C7" t="n">
-        <v>173.910715321097</v>
+        <v>127.498592602829</v>
       </c>
       <c r="D7" t="n">
-        <v>34.85400699617026</v>
+        <v>36.4110588551057</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.922082078466008</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C8" t="n">
-        <v>87.12029127486194</v>
+        <v>59.49881961587794</v>
       </c>
       <c r="D8" t="n">
-        <v>31.79389940203295</v>
+        <v>31.29320807286708</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>1.109374905798895</v>
       </c>
       <c r="C9" t="n">
-        <v>30.50780990946962</v>
+        <v>32.17187226816797</v>
       </c>
       <c r="D9" t="n">
-        <v>31.8390597964283</v>
+        <v>26.40312275801371</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>25.76596849795754</v>
+        <v>24.91184799526281</v>
       </c>
       <c r="D10" t="n">
-        <v>23.63066724122073</v>
+        <v>26.05067533218912</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>20.43507846389736</v>
+        <v>20.96816746730337</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>23.81130881880213</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.62156946997525</v>
+        <v>16.48943444052943</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>20.17786056538469</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>13.78864650614645</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>27.04125876577415</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>8.296749848589794</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.541826921753</v>
+        <v>34.40043955680824</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.42788743479814</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.055779692692821</v>
+        <v>0.3603014074585794</v>
       </c>
       <c r="C2" t="n">
-        <v>9.749736450875075</v>
+        <v>2.178498155723672</v>
       </c>
       <c r="D2" t="n">
-        <v>16.29995713360979</v>
+        <v>8.524515315975055</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.26908098642164</v>
+        <v>3.254493639578176</v>
       </c>
       <c r="C3" t="n">
-        <v>19.10481032464293</v>
+        <v>12.82653375598458</v>
       </c>
       <c r="D3" t="n">
-        <v>80.85183218324607</v>
+        <v>64.13757751844412</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.9495963763807</v>
+        <v>12.5585166327252</v>
       </c>
       <c r="C4" t="n">
-        <v>89.33904108645974</v>
+        <v>52.27610175573416</v>
       </c>
       <c r="D4" t="n">
-        <v>155.2329652478014</v>
+        <v>144.984500963169</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.58330667170541</v>
+        <v>19.34042977366217</v>
       </c>
       <c r="C5" t="n">
-        <v>215.1745530782947</v>
+        <v>144.586893142949</v>
       </c>
       <c r="D5" t="n">
-        <v>132.4623089955009</v>
+        <v>139.3590866178347</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.06548366321083</v>
+        <v>12.15600007398401</v>
       </c>
       <c r="C6" t="n">
-        <v>290.657207067015</v>
+        <v>226.5765709154171</v>
       </c>
       <c r="D6" t="n">
-        <v>69.23284810348508</v>
+        <v>75.39135145222532</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.21119892960008</v>
+        <v>3.892629647338603</v>
       </c>
       <c r="C7" t="n">
-        <v>247.0921526910627</v>
+        <v>165.6463631467473</v>
       </c>
       <c r="D7" t="n">
-        <v>40.36357511240336</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.090361846519712</v>
+        <v>1.084831213192726</v>
       </c>
       <c r="C8" t="n">
-        <v>143.5315143608837</v>
+        <v>67.5098808825319</v>
       </c>
       <c r="D8" t="n">
-        <v>33.54631905411351</v>
+        <v>26.95388322009618</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>58.13124506386212</v>
+        <v>30.06405994715006</v>
       </c>
       <c r="D9" t="n">
-        <v>32.72655972106742</v>
+        <v>20.85624822901923</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>30.03657101143117</v>
+        <v>18.07888397370501</v>
       </c>
       <c r="D10" t="n">
-        <v>24.91184799526281</v>
+        <v>19.78712497909446</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.81130881880213</v>
+        <v>13.50492141961912</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>17.41424077792992</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.00819813899924</v>
+        <v>11.71617710248143</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>15.34962535589888</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>8.065057390387548</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.82791641431633</v>
+        <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>2.765583282863265</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>11.46681318560274</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.97231544229862</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.99988649347554</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.557051858935441</v>
+        <v>0.8452847733565036</v>
       </c>
       <c r="C2" t="n">
-        <v>4.988260085278044</v>
+        <v>4.811545498513618</v>
       </c>
       <c r="D2" t="n">
-        <v>12.63705644906494</v>
+        <v>12.11280317499715</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.007535186464485</v>
+        <v>2.159844949342983</v>
       </c>
       <c r="C3" t="n">
-        <v>27.9798095710341</v>
+        <v>10.22490233973053</v>
       </c>
       <c r="D3" t="n">
-        <v>77.30281423239386</v>
+        <v>56.07252012805658</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.15906849028376</v>
+        <v>9.265734832681398</v>
       </c>
       <c r="C4" t="n">
-        <v>73.57708169477721</v>
+        <v>40.64926369433918</v>
       </c>
       <c r="D4" t="n">
-        <v>158.8575777718806</v>
+        <v>144.7547720003752</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.77398671050754</v>
+        <v>19.61041039233004</v>
       </c>
       <c r="C5" t="n">
-        <v>203.54084278297</v>
+        <v>119.2823460659875</v>
       </c>
       <c r="D5" t="n">
-        <v>147.2376119444154</v>
+        <v>160.5402933369597</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.90197376495812</v>
+        <v>19.15978819608075</v>
       </c>
       <c r="C6" t="n">
-        <v>321.4899754665903</v>
+        <v>229.4344384824796</v>
       </c>
       <c r="D6" t="n">
-        <v>83.20017269180445</v>
+        <v>100.7901463087946</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>13.65414707066464</v>
+        <v>8.803331663981149</v>
       </c>
       <c r="C7" t="n">
-        <v>307.5177421397496</v>
+        <v>252.841267247132</v>
       </c>
       <c r="D7" t="n">
-        <v>44.91495746929157</v>
+        <v>48.02906118716245</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.172427743048944</v>
+        <v>2.420008090968388</v>
       </c>
       <c r="C8" t="n">
-        <v>187.7592484372025</v>
+        <v>144.9501397935203</v>
       </c>
       <c r="D8" t="n">
-        <v>34.79804737702819</v>
+        <v>30.20837685967435</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.664062358698343</v>
+        <v>0.6656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>66.78436932909349</v>
+        <v>56.57812019574367</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>22.96406055003713</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>31.03304493124168</v>
+        <v>26.76244241776806</v>
       </c>
       <c r="D10" t="n">
-        <v>25.33890824661018</v>
+        <v>20.35653864755762</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>16.8811517745239</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>18.12502611580461</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.92336692580652</v>
+        <v>13.66887328622834</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>14.10280577150543</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>11.44717823151781</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>8.585383673638358</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>3.072870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.956623174563893</v>
+        <v>0.8168140899333463</v>
       </c>
       <c r="C2" t="n">
-        <v>7.508406442079605</v>
+        <v>10.00302735857075</v>
       </c>
       <c r="D2" t="n">
-        <v>14.87053247622644</v>
+        <v>23.96642495607313</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>7.225663103256524</v>
+        <v>2.547635292520473</v>
       </c>
       <c r="C3" t="n">
-        <v>24.08717992369549</v>
+        <v>15.0060136594125</v>
       </c>
       <c r="D3" t="n">
-        <v>70.66129101316419</v>
+        <v>52.85729639664827</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.47515019332223</v>
+        <v>6.598326320242813</v>
       </c>
       <c r="C4" t="n">
-        <v>71.70096183196155</v>
+        <v>32.25139383221197</v>
       </c>
       <c r="D4" t="n">
-        <v>160.0827989067807</v>
+        <v>140.5303116290012</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.27682146153116</v>
+        <v>17.20512851692536</v>
       </c>
       <c r="C5" t="n">
-        <v>174.8738098189631</v>
+        <v>96.26036240139979</v>
       </c>
       <c r="D5" t="n">
-        <v>164.0254976870359</v>
+        <v>173.3275571847744</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.06676851055134</v>
+        <v>22.94344384824796</v>
       </c>
       <c r="C6" t="n">
-        <v>323.4623066044222</v>
+        <v>210.7979218127624</v>
       </c>
       <c r="D6" t="n">
-        <v>101.8769410173958</v>
+        <v>125.907179574245</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.09248957284423</v>
+        <v>15.39085875947725</v>
       </c>
       <c r="C7" t="n">
-        <v>369.3207236174948</v>
+        <v>294.3426879487574</v>
       </c>
       <c r="D7" t="n">
-        <v>53.71828913327272</v>
+        <v>63.47980655659876</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.260024272905162</v>
+        <v>5.591053175685585</v>
       </c>
       <c r="C8" t="n">
-        <v>272.0422888467912</v>
+        <v>238.3290726829557</v>
       </c>
       <c r="D8" t="n">
-        <v>37.38495257771854</v>
+        <v>34.96494448675015</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>1.442187377538564</v>
       </c>
       <c r="C9" t="n">
-        <v>124.0281144683165</v>
+        <v>115.1531152219253</v>
       </c>
       <c r="D9" t="n">
-        <v>33.28124717396686</v>
+        <v>25.18281036163492</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7117670855789376</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>47.68839473378882</v>
+        <v>45.55309347705201</v>
       </c>
       <c r="D10" t="n">
-        <v>26.47773558353648</v>
+        <v>21.35301256736813</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.54293184264426</v>
+        <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>18.65811511921063</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D12" t="n">
-        <v>20.39482680802324</v>
+        <v>14.97067074205961</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>14.82929907264807</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>9.365873098514571</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.98419422574081</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>3.68744437715102</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>8.241771977151972</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>27.69215749368978</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.111559385385641</v>
+        <v>7.24529805734146</v>
       </c>
       <c r="C2" t="n">
-        <v>5.002986300841745</v>
+        <v>10.36431051373358</v>
       </c>
       <c r="D2" t="n">
-        <v>9.191122007158638</v>
+        <v>13.38711169510951</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.413716694115407</v>
+        <v>0.8541205026947251</v>
       </c>
       <c r="C2" t="n">
-        <v>4.384485247166255</v>
+        <v>11.00931875542373</v>
       </c>
       <c r="D2" t="n">
-        <v>11.06331487915731</v>
+        <v>19.58292145661112</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.807659565425636</v>
+        <v>2.606540154775281</v>
       </c>
       <c r="C3" t="n">
-        <v>29.1480893390878</v>
+        <v>27.09623663721197</v>
       </c>
       <c r="D3" t="n">
-        <v>76.13453446434015</v>
+        <v>57.96238445873169</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.51941095547134</v>
+        <v>5.679410469067798</v>
       </c>
       <c r="C4" t="n">
-        <v>103.9140675037079</v>
+        <v>34.3827680981318</v>
       </c>
       <c r="D4" t="n">
-        <v>163.3883434269797</v>
+        <v>134.4297313948115</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.44613973055134</v>
+        <v>14.21079801897258</v>
       </c>
       <c r="C5" t="n">
-        <v>267.3544435590127</v>
+        <v>78.78525326580655</v>
       </c>
       <c r="D5" t="n">
-        <v>149.1274762750905</v>
+        <v>182.924140993787</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>15.57739082328414</v>
+        <v>23.18495378349268</v>
       </c>
       <c r="C6" t="n">
-        <v>303.4572336349849</v>
+        <v>183.8695640329767</v>
       </c>
       <c r="D6" t="n">
-        <v>79.69827863075608</v>
+        <v>145.7914975760599</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4.790928796724434</v>
+        <v>20.72076704583318</v>
       </c>
       <c r="C7" t="n">
-        <v>191.277832209223</v>
+        <v>302.487266903189</v>
       </c>
       <c r="D7" t="n">
-        <v>33.11729530735765</v>
+        <v>81.02658327460199</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.585522542358599</v>
+        <v>10.18072369303942</v>
       </c>
       <c r="C8" t="n">
-        <v>91.37616757277186</v>
+        <v>308.9265500953438</v>
       </c>
       <c r="D8" t="n">
-        <v>24.53387512912779</v>
+        <v>41.55738032076748</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4437499623195582</v>
+        <v>3.106249736236907</v>
       </c>
       <c r="C9" t="n">
-        <v>36.38749691020377</v>
+        <v>193.0312336090078</v>
       </c>
       <c r="D9" t="n">
-        <v>20.1906232855399</v>
+        <v>27.84531013555227</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
-        <v>21.49536598448391</v>
+        <v>84.55792976677779</v>
       </c>
       <c r="D10" t="n">
-        <v>19.21771131063132</v>
+        <v>22.49183990429443</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.81497376771187</v>
+        <v>35.36157055926586</v>
       </c>
       <c r="D11" t="n">
-        <v>16.34806277111788</v>
+        <v>19.19120412261664</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.63134588928871</v>
+        <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
-        <v>13.4519070435898</v>
+        <v>15.62156946997525</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>16.1301147807751</v>
+      </c>
+      <c r="D13" t="n">
         <v>9.886199381765381</v>
-      </c>
-      <c r="D13" t="n">
-        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>4.302018440009523</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>11.46681318560274</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>0.3583379120500857</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.482079180514189</v>
+        <v>5.41433858892116</v>
       </c>
       <c r="C2" t="n">
-        <v>6.172247816599698</v>
+        <v>10.09334814736146</v>
       </c>
       <c r="D2" t="n">
-        <v>22.35635872110836</v>
+        <v>22.0677248960598</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>8.742463306317847</v>
+        <v>11.66807146497334</v>
       </c>
       <c r="C3" t="n">
-        <v>12.80689880189964</v>
+        <v>20.46453089502477</v>
       </c>
       <c r="D3" t="n">
-        <v>10.85812960896972</v>
+        <v>12.13931036301181</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>3.632466505713199</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>8.29576810088555</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>14.32958949118645</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.78007281871549</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39886016340244</v>
+        <v>11.67721265128257</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14697379663629</v>
+        <v>59.94302494325054</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576336489812051</v>
+        <v>0.7784808434188382</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.070325981807276</v>
+        <v>2.604576659366788</v>
       </c>
       <c r="C2" t="n">
-        <v>4.630903920932204</v>
+        <v>6.016149931624454</v>
       </c>
       <c r="D2" t="n">
-        <v>21.98427634119883</v>
+        <v>24.97075285751762</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.82929907264807</v>
+        <v>16.26755945936965</v>
       </c>
       <c r="C3" t="n">
-        <v>19.8509385798705</v>
+        <v>32.90818304635308</v>
       </c>
       <c r="D3" t="n">
-        <v>27.01278808235099</v>
+        <v>28.50504459280614</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>10.29951516525329</v>
+        <v>14.33253473429918</v>
       </c>
       <c r="C4" t="n">
-        <v>20.05023336383261</v>
+        <v>33.31069960509428</v>
       </c>
       <c r="D4" t="n">
-        <v>20.76494569252429</v>
+        <v>20.65008121112741</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>2.454369260617026</v>
       </c>
       <c r="C5" t="n">
-        <v>5.399612373357458</v>
+        <v>5.129631754689585</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>25.72178985126644</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>5.514476854754335</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>13.72581465307466</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>30.06798693796707</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>6.827073535332318</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.22360179685679</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>6.842781498600267</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>20.36144738607885</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>20.85624822901923</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>22.91890015564179</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>24.87748682561417</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.57268737340794</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>40.32528695193774</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44254932285268</v>
+        <v>13.62545008004338</v>
       </c>
       <c r="C21" t="n">
-        <v>86.15316990644126</v>
+        <v>73.73772984494063</v>
       </c>
       <c r="D21" t="n">
-        <v>3.251063015337406</v>
+        <v>1.602994127063927</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.853359739168731</v>
+        <v>2.818597658892593</v>
       </c>
       <c r="C2" t="n">
-        <v>11.08589507635498</v>
+        <v>3.53330998758427</v>
       </c>
       <c r="D2" t="n">
-        <v>22.54681777573225</v>
+        <v>26.65935890882214</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.41696503686441</v>
+        <v>12.10004045484194</v>
       </c>
       <c r="C3" t="n">
-        <v>18.74156367407161</v>
+        <v>26.92443078896877</v>
       </c>
       <c r="D3" t="n">
-        <v>38.33233911231671</v>
+        <v>42.59312414874787</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>20.65008121112741</v>
+        <v>24.47889725768997</v>
       </c>
       <c r="C4" t="n">
-        <v>37.50963453615788</v>
+        <v>63.71149901480101</v>
       </c>
       <c r="D4" t="n">
-        <v>29.62227348023901</v>
+        <v>30.79644373451819</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>9.621127501618743</v>
+        <v>12.90998231084556</v>
       </c>
       <c r="C5" t="n">
-        <v>23.36559536107409</v>
+        <v>38.9508401659922</v>
       </c>
       <c r="D5" t="n">
-        <v>29.89421759431538</v>
+        <v>27.36621725587985</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.916993413495527</v>
+        <v>4.508185457901354</v>
       </c>
       <c r="C6" t="n">
-        <v>12.19625172985813</v>
+        <v>10.58618549489336</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>31.95981476405067</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>7.006733365209485</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.82246789644735</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42913122440964</v>
+        <v>32.81786225756237</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>7.42692138262712</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>23.699389580518</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>34.29735604786232</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>29.50937249425062</v>
+        <v>23.96249796525614</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>36.0546844384641</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.537678946757763</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.69897297435728</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>6.219371706403542</v>
       </c>
       <c r="C11" t="n">
-        <v>31.27455486648638</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.95717262057418</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77987719673301</v>
+        <v>41.44055234396211</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.52854978444583</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>24.72531593145592</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73844290794894</v>
+        <v>14.83080907399497</v>
       </c>
       <c r="C21" t="n">
-        <v>102.1045017384885</v>
+        <v>87.33698676908151</v>
       </c>
       <c r="D21" t="n">
-        <v>5.021532872384681</v>
+        <v>2.471801512332495</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.997095814616265</v>
+        <v>2.4160811001514</v>
       </c>
       <c r="C2" t="n">
-        <v>10.29067943591507</v>
+        <v>4.962734644967626</v>
       </c>
       <c r="D2" t="n">
-        <v>18.41856867937441</v>
+        <v>32.6588191294744</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.75428533649781</v>
+        <v>10.77958979262998</v>
       </c>
       <c r="C3" t="n">
-        <v>32.74619467515236</v>
+        <v>18.93300447639974</v>
       </c>
       <c r="D3" t="n">
-        <v>46.94226647856124</v>
+        <v>54.03539364174444</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.68310078017331</v>
+        <v>24.18535469412017</v>
       </c>
       <c r="C4" t="n">
-        <v>42.39775635560276</v>
+        <v>65.94497504196249</v>
       </c>
       <c r="D4" t="n">
-        <v>41.21082338116835</v>
+        <v>45.20555478974863</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>20.19945901487813</v>
+        <v>25.40272184738622</v>
       </c>
       <c r="C5" t="n">
-        <v>48.62105505282329</v>
+        <v>83.86579763528378</v>
       </c>
       <c r="D5" t="n">
-        <v>33.91938318172731</v>
+        <v>32.07860623626453</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>9.499390786292139</v>
+        <v>11.10945702125691</v>
       </c>
       <c r="C6" t="n">
-        <v>25.318291544821</v>
+        <v>38.60133798328035</v>
       </c>
       <c r="D6" t="n">
-        <v>38.23907308041327</v>
+        <v>33.85164259013428</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.467753875577986</v>
       </c>
       <c r="C7" t="n">
-        <v>21.02020009562846</v>
+        <v>17.66654993792135</v>
       </c>
       <c r="D7" t="n">
-        <v>39.46527596301753</v>
+        <v>35.03366682604743</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>7.760715602071035</v>
       </c>
       <c r="C8" t="n">
-        <v>31.87734795689393</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>35.46563581591602</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>7.876561831172157</v>
       </c>
       <c r="C9" t="n">
-        <v>34.27968458918587</v>
+        <v>27.5124976638126</v>
       </c>
       <c r="D9" t="n">
-        <v>41.93437143919824</v>
+        <v>37.27499683484289</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
-        <v>33.16834618797849</v>
+        <v>27.47420950334699</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.4142661401257</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9.062513057902304</v>
+        <v>6.574764375340887</v>
       </c>
       <c r="C11" t="n">
-        <v>33.7623035490478</v>
+        <v>28.25371718051895</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>45.4902616239802</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>34.49763257952867</v>
+        <v>28.8565102709265</v>
       </c>
       <c r="D12" t="n">
-        <v>46.86470840992573</v>
+        <v>42.95931604243193</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>33.04071898642641</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="D13" t="n">
-        <v>46.30903920932205</v>
+        <v>41.62610266006477</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>29.02537087605695</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>37.77765165941727</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.06773558664349</v>
+        <v>16.06560995777019</v>
       </c>
       <c r="C21" t="n">
-        <v>117.870465493817</v>
+        <v>100.6214518407712</v>
       </c>
       <c r="D21" t="n">
-        <v>6.882946890149898</v>
+        <v>3.38223367532004</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.866924280578939</v>
+        <v>1.978221624057323</v>
       </c>
       <c r="C2" t="n">
-        <v>9.450303401079797</v>
+        <v>7.035204048632643</v>
       </c>
       <c r="D2" t="n">
-        <v>25.25644143945344</v>
+        <v>39.9973832187193</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.1273494641116</v>
+        <v>9.400234268163208</v>
       </c>
       <c r="C3" t="n">
-        <v>34.6556939599124</v>
+        <v>19.09499284760046</v>
       </c>
       <c r="D3" t="n">
-        <v>47.51168014702439</v>
+        <v>66.83738370512286</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>18.63357142660446</v>
+        <v>22.51343835378785</v>
       </c>
       <c r="C4" t="n">
-        <v>53.71828913327272</v>
+        <v>55.73479891779567</v>
       </c>
       <c r="D4" t="n">
-        <v>47.38797993628929</v>
+        <v>61.21000586438014</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>17.57328390601791</v>
+        <v>30.80233422074368</v>
       </c>
       <c r="C5" t="n">
-        <v>48.22835597112457</v>
+        <v>103.1571400237336</v>
       </c>
       <c r="D5" t="n">
-        <v>33.35487825178539</v>
+        <v>40.57072387799944</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.18366893615217</v>
+        <v>22.58117894538089</v>
       </c>
       <c r="C6" t="n">
-        <v>35.34095385747668</v>
+        <v>87.54735152620934</v>
       </c>
       <c r="D6" t="n">
-        <v>31.35603992593888</v>
+        <v>36.10573531908495</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.030475236560656</v>
+        <v>9.82140403328509</v>
       </c>
       <c r="C7" t="n">
-        <v>18.74450891718435</v>
+        <v>37.12969817461437</v>
       </c>
       <c r="D7" t="n">
-        <v>30.72183090899544</v>
+        <v>37.18958478457343</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>7.760715602071035</v>
       </c>
       <c r="C8" t="n">
-        <v>18.69247628885927</v>
+        <v>25.11801501315464</v>
       </c>
       <c r="D8" t="n">
-        <v>30.37527396939631</v>
+        <v>36.80081269369168</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>8.098436812331936</v>
       </c>
       <c r="C9" t="n">
-        <v>21.96562313481813</v>
+        <v>30.39687241888974</v>
       </c>
       <c r="D9" t="n">
-        <v>29.95312245657017</v>
+        <v>38.38437174064178</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>7.971791358484101</v>
       </c>
       <c r="C10" t="n">
-        <v>21.49536598448391</v>
+        <v>30.46363126277853</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>44.4142661401257</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>7.107853378746905</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>30.74146586308036</v>
       </c>
       <c r="D11" t="n">
-        <v>34.47308888692249</v>
+        <v>45.84565429291754</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>5.858088551240717</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>31.02617269731195</v>
       </c>
       <c r="D12" t="n">
-        <v>32.11100391050467</v>
+        <v>44.04414725562465</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>30.69925071179776</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>41.88626580169016</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>28.88498095434966</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.605157496443535</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>35.64235040268044</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.063278376576924</v>
+        <v>17.32313760004832</v>
       </c>
       <c r="C21" t="n">
-        <v>66.21823478040865</v>
+        <v>114.3327081603189</v>
       </c>
       <c r="D21" t="n">
-        <v>5.297458782432693</v>
+        <v>4.33078440001208</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.138467484027806</v>
+        <v>2.268818944514379</v>
       </c>
       <c r="C2" t="n">
-        <v>6.508987279156353</v>
+        <v>10.7255936688964</v>
       </c>
       <c r="D2" t="n">
-        <v>30.63740060643021</v>
+        <v>31.3629121598686</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.09361018926871</v>
+        <v>7.966882619962866</v>
       </c>
       <c r="C3" t="n">
-        <v>36.1675854244525</v>
+        <v>23.61103228713579</v>
       </c>
       <c r="D3" t="n">
-        <v>57.80039608753097</v>
+        <v>82.04956438242718</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.36403277629309</v>
+        <v>20.26719960647115</v>
       </c>
       <c r="C4" t="n">
-        <v>74.95545547153972</v>
+        <v>51.05088062083414</v>
       </c>
       <c r="D4" t="n">
-        <v>62.02681995431348</v>
+        <v>77.12511789792518</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>23.6846633649543</v>
+        <v>32.17678100668922</v>
       </c>
       <c r="C5" t="n">
-        <v>79.98789420350889</v>
+        <v>102.9362467902781</v>
       </c>
       <c r="D5" t="n">
-        <v>43.98229715025711</v>
+        <v>51.90990986205011</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>18.19374845510189</v>
+        <v>31.396291581813</v>
       </c>
       <c r="C6" t="n">
-        <v>60.09572222006002</v>
+        <v>124.2568616834061</v>
       </c>
       <c r="D6" t="n">
-        <v>35.05919226635785</v>
+        <v>39.92964262712628</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.222537933694536</v>
+        <v>17.78632315783946</v>
       </c>
       <c r="C7" t="n">
-        <v>37.96811071404115</v>
+        <v>78.69100548619885</v>
       </c>
       <c r="D7" t="n">
-        <v>33.47661496711198</v>
+        <v>39.34550274309942</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.424156065963627</v>
+        <v>9.262789589568655</v>
       </c>
       <c r="C8" t="n">
-        <v>22.69800692218626</v>
+        <v>36.80081269369168</v>
       </c>
       <c r="D8" t="n">
-        <v>32.3780392860598</v>
+        <v>38.21943812632832</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>8.320311793491715</v>
       </c>
       <c r="C9" t="n">
-        <v>23.40781051235669</v>
+        <v>31.61718481526852</v>
       </c>
       <c r="D9" t="n">
-        <v>31.17343485294896</v>
+        <v>39.49374664644068</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>8.114144775599888</v>
       </c>
       <c r="C10" t="n">
-        <v>24.76949457814703</v>
+        <v>33.45305302221006</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>44.55661955724149</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>46.02335062738621</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>21.91359050649305</v>
+        <v>33.41280136633594</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>44.91201222617883</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>21.33337761328319</v>
+        <v>32.5203927031756</v>
       </c>
       <c r="D13" t="n">
-        <v>31.21957699504857</v>
+        <v>42.14642894331557</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>31.34327720578367</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>42.09832330580748</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.43836786437537</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>24.07245370813179</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>35.64235040268044</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.286792272936624</v>
+        <v>17.71096701917932</v>
       </c>
       <c r="C21" t="n">
-        <v>75.60046983171748</v>
+        <v>126.6334141871322</v>
       </c>
       <c r="D21" t="n">
-        <v>6.375943238819546</v>
+        <v>5.313290105753798</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.632466505713198</v>
+        <v>2.086213871524472</v>
       </c>
       <c r="C2" t="n">
-        <v>7.152032025438014</v>
+        <v>6.692574099850506</v>
       </c>
       <c r="D2" t="n">
-        <v>21.80854350213865</v>
+        <v>24.90301226592459</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.93162181806799</v>
+        <v>12.07058802371454</v>
       </c>
       <c r="C3" t="n">
-        <v>29.5947845445201</v>
+        <v>38.88702656521616</v>
       </c>
       <c r="D3" t="n">
-        <v>68.89905388404115</v>
+        <v>87.95477682347175</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.63052837250048</v>
+        <v>15.45565410795754</v>
       </c>
       <c r="C4" t="n">
-        <v>84.19566486391069</v>
+        <v>82.74071476621694</v>
       </c>
       <c r="D4" t="n">
-        <v>77.07406701730434</v>
+        <v>70.70546965985528</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.55689729468198</v>
+        <v>17.67145867644259</v>
       </c>
       <c r="C5" t="n">
-        <v>113.4164035331128</v>
+        <v>74.24467013366505</v>
       </c>
       <c r="D5" t="n">
-        <v>55.93507544946203</v>
+        <v>38.80357801035519</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>25.92206638293279</v>
+        <v>11.02895370950867</v>
       </c>
       <c r="C6" t="n">
-        <v>96.32221250676733</v>
+        <v>51.80388110999145</v>
       </c>
       <c r="D6" t="n">
-        <v>41.29819892684633</v>
+        <v>25.88181472705867</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.81006502919063</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>65.15663163545231</v>
+        <v>25.87101550231194</v>
       </c>
       <c r="D7" t="n">
-        <v>36.05173919535137</v>
+        <v>26.82920126165683</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.011061266653972</v>
+        <v>5.757950285407543</v>
       </c>
       <c r="C8" t="n">
-        <v>38.05254101660637</v>
+        <v>23.28214680621311</v>
       </c>
       <c r="D8" t="n">
-        <v>34.54770171244525</v>
+        <v>29.04009709162065</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.546874528994477</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>26.62499773917349</v>
+        <v>25.5156228333746</v>
       </c>
       <c r="D9" t="n">
-        <v>32.72655972106742</v>
+        <v>33.9468721174462</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>26.90479583488384</v>
+        <v>26.33538216642069</v>
       </c>
       <c r="D10" t="n">
-        <v>34.30717352490479</v>
+        <v>36.01541453029424</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.264712027248144</v>
+        <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>26.4698816019025</v>
       </c>
       <c r="D12" t="n">
-        <v>34.06370009425158</v>
+        <v>34.28066633689012</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>25.75615102091507</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>34.86186097780424</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>34.10886048864694</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>32.6087499965578</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>30.17205219461722</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>25.97213551584937</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>30.69237847786803</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>13.23984953947248</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>13.4499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>96.16709636949629</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.496401793533127</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>85.27157040143932</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.496401793533127</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
